--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Joventut Badalona.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2098.079999999999</v>
+        <v>2398.76</v>
       </c>
       <c r="C2" t="n">
-        <v>2096.920000000001</v>
+        <v>2400.66</v>
       </c>
       <c r="D2" t="n">
-        <v>112.4506418938252</v>
+        <v>114.2602450992644</v>
       </c>
       <c r="E2" t="n">
-        <v>108.3970776186025</v>
+        <v>108.5118259145402</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5257816785518377</v>
+        <v>0.5335731414868106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1341063188231962</v>
+        <v>0.1305730625583567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3020937188434696</v>
+        <v>0.3003502626970228</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2419089413055403</v>
+        <v>0.2484412470023981</v>
       </c>
       <c r="J2" t="n">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="K2" t="n">
-        <v>275</v>
+        <v>332</v>
       </c>
       <c r="L2" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="M2" t="n">
+        <v>334</v>
+      </c>
+      <c r="N2" t="n">
+        <v>934</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1274</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.6110311750599521</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>184</v>
+      </c>
+      <c r="R2" t="n">
+        <v>398</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1908872901678657</v>
+      </c>
+      <c r="T2" t="n">
+        <v>115</v>
+      </c>
+      <c r="U2" t="n">
         <v>298</v>
       </c>
-      <c r="N2" t="n">
-        <v>803</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1102</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.6044980800877674</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>170</v>
-      </c>
-      <c r="R2" t="n">
-        <v>364</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1996708721886999</v>
-      </c>
-      <c r="T2" t="n">
-        <v>92</v>
-      </c>
-      <c r="U2" t="n">
-        <v>247</v>
-      </c>
       <c r="V2" t="n">
-        <v>0.1354909489851892</v>
+        <v>0.1429256594724221</v>
       </c>
       <c r="W2" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="X2" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09215578716401536</v>
+        <v>0.09160671462829736</v>
       </c>
       <c r="Z2" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="AA2" t="n">
-        <v>524</v>
+        <v>603</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2874382885353812</v>
+        <v>0.2892086330935252</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7286751361161524</v>
+        <v>0.7331240188383046</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.467032967032967</v>
+        <v>0.4623115577889447</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3724696356275304</v>
+        <v>0.3859060402684564</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3717277486910995</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3110687022900763</v>
+        <v>0.3217247097844113</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.457350272232305</v>
+        <v>1.466248037676609</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7449392712550608</v>
+        <v>0.7718120805369127</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9667630057803468</v>
+        <v>1.001259445843829</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7537537537537538</v>
+        <v>0.7560321715817694</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9075907590759076</v>
+        <v>0.967930029154519</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.59</v>
+        <v>1.603448275862069</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.546583850931677</v>
+        <v>1.611731843575419</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.661490683229814</v>
+        <v>5.824022346368715</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.208074534161491</v>
+        <v>7.435754189944134</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.93142857142855</v>
+        <v>74.96124999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>74.89000000000001</v>
+        <v>75.02062500000001</v>
       </c>
       <c r="D3" t="n">
-        <v>112.4506418938252</v>
+        <v>114.2602450992644</v>
       </c>
       <c r="E3" t="n">
-        <v>108.3970776186025</v>
+        <v>108.5118259145402</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5257816785518376</v>
+        <v>0.5335731414868106</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1341063188231962</v>
+        <v>0.1305730625583567</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3020937188434696</v>
+        <v>0.3003502626970228</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2419089413055403</v>
+        <v>0.2484412470023981</v>
       </c>
       <c r="J3" t="n">
-        <v>8.964285714285714</v>
+        <v>8.8125</v>
       </c>
       <c r="K3" t="n">
-        <v>9.821428571428571</v>
+        <v>10.375</v>
       </c>
       <c r="L3" t="n">
-        <v>5.678571428571429</v>
+        <v>5.8125</v>
       </c>
       <c r="M3" t="n">
-        <v>10.64285714285714</v>
+        <v>10.4375</v>
       </c>
       <c r="N3" t="n">
-        <v>28.67857142857143</v>
+        <v>29.1875</v>
       </c>
       <c r="O3" t="n">
-        <v>39.35714285714285</v>
+        <v>39.8125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6044980800877673</v>
+        <v>0.6110311750599521</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.071428571428571</v>
+        <v>5.75</v>
       </c>
       <c r="R3" t="n">
-        <v>13</v>
+        <v>12.4375</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1996708721886999</v>
+        <v>0.1908872901678657</v>
       </c>
       <c r="T3" t="n">
-        <v>3.285714285714286</v>
+        <v>3.59375</v>
       </c>
       <c r="U3" t="n">
-        <v>8.821428571428571</v>
+        <v>9.3125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1354909489851892</v>
+        <v>0.1429256594724221</v>
       </c>
       <c r="W3" t="n">
-        <v>2.142857142857143</v>
+        <v>2.21875</v>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>5.96875</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09215578716401536</v>
+        <v>0.09160671462829736</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.821428571428571</v>
+        <v>6.0625</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.71428571428572</v>
+        <v>18.84375</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2874382885353812</v>
+        <v>0.2892086330935252</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7286751361161524</v>
+        <v>0.7331240188383046</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.467032967032967</v>
+        <v>0.4623115577889447</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3724696356275304</v>
+        <v>0.3859060402684564</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3717277486910995</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3110687022900763</v>
+        <v>0.3217247097844113</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.457350272232305</v>
+        <v>1.466248037676609</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7449392712550608</v>
+        <v>0.7718120805369127</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9667630057803466</v>
+        <v>1.001259445843829</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7537537537537538</v>
+        <v>0.7560321715817694</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.9075907590759076</v>
+        <v>0.967930029154519</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.59</v>
+        <v>1.603448275862069</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.546583850931677</v>
+        <v>1.611731843575419</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.661490683229814</v>
+        <v>5.824022346368715</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.20807453416149</v>
+        <v>7.435754189944134</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2095.76</v>
+        <v>2402.56</v>
       </c>
       <c r="C4" t="n">
-        <v>2096.920000000001</v>
+        <v>2400.66</v>
       </c>
       <c r="D4" t="n">
-        <v>108.3970776186025</v>
+        <v>108.5118259145402</v>
       </c>
       <c r="E4" t="n">
-        <v>112.4506418938252</v>
+        <v>114.2602450992644</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5016629711751663</v>
+        <v>0.5036040365209035</v>
       </c>
       <c r="G4" t="n">
-        <v>0.138590620786096</v>
+        <v>0.1356087487638881</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2971926427879961</v>
+        <v>0.292191435768262</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2566518847006652</v>
+        <v>0.2445939452186449</v>
       </c>
       <c r="J4" t="n">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="K4" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="L4" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="N4" t="n">
-        <v>789</v>
+        <v>884</v>
       </c>
       <c r="O4" t="n">
-        <v>1079</v>
+        <v>1217</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5981152993348116</v>
+        <v>0.5848149927919269</v>
       </c>
       <c r="Q4" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="R4" t="n">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1779379157427938</v>
+        <v>0.1720326765977895</v>
       </c>
       <c r="T4" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="U4" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1358093126385809</v>
+        <v>0.1345506967803941</v>
       </c>
       <c r="W4" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="X4" t="n">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1014412416851441</v>
+        <v>0.1081210956271024</v>
       </c>
       <c r="Z4" t="n">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="AA4" t="n">
-        <v>580</v>
+        <v>675</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3215077605321508</v>
+        <v>0.3243632868813071</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7312326227988879</v>
+        <v>0.7263763352506163</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3738317757009346</v>
+        <v>0.3798882681564246</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3183673469387755</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3879781420765027</v>
+        <v>0.3733333333333334</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3155172413793104</v>
+        <v>0.3170370370370371</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.462465245597776</v>
+        <v>1.452752670501233</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.636734693877551</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9986893840104849</v>
+        <v>0.9933333333333333</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.84472049689441</v>
+        <v>0.8603351955307262</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9087947882736156</v>
+        <v>0.8908045977011494</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.74390243902439</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.357357357357357</v>
+        <v>1.399463806970509</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.417417417417417</v>
+        <v>5.579088471849866</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.774774774774775</v>
+        <v>6.978552278820375</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.84857142857142</v>
+        <v>75.08</v>
       </c>
       <c r="C5" t="n">
-        <v>74.89000000000001</v>
+        <v>75.02062500000001</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3970776186025</v>
+        <v>108.5118259145402</v>
       </c>
       <c r="E5" t="n">
-        <v>112.4506418938252</v>
+        <v>114.2602450992644</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5016629711751662</v>
+        <v>0.5036040365209035</v>
       </c>
       <c r="G5" t="n">
-        <v>0.138590620786096</v>
+        <v>0.1356087487638881</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2971926427879961</v>
+        <v>0.292191435768262</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2566518847006652</v>
+        <v>0.2445939452186449</v>
       </c>
       <c r="J5" t="n">
-        <v>9.714285714285714</v>
+        <v>9.625</v>
       </c>
       <c r="K5" t="n">
-        <v>9.964285714285714</v>
+        <v>9.6875</v>
       </c>
       <c r="L5" t="n">
-        <v>5.107142857142857</v>
+        <v>4.875</v>
       </c>
       <c r="M5" t="n">
-        <v>11.21428571428571</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>28.17857142857143</v>
+        <v>27.625</v>
       </c>
       <c r="O5" t="n">
-        <v>38.53571428571428</v>
+        <v>38.03125</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5981152993348114</v>
+        <v>0.5848149927919269</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.285714285714286</v>
+        <v>4.25</v>
       </c>
       <c r="R5" t="n">
-        <v>11.46428571428571</v>
+        <v>11.1875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1779379157427938</v>
+        <v>0.1720326765977895</v>
       </c>
       <c r="T5" t="n">
-        <v>2.785714285714286</v>
+        <v>2.8125</v>
       </c>
       <c r="U5" t="n">
         <v>8.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1358093126385809</v>
+        <v>0.1345506967803941</v>
       </c>
       <c r="W5" t="n">
-        <v>2.535714285714286</v>
+        <v>2.625</v>
       </c>
       <c r="X5" t="n">
-        <v>6.535714285714286</v>
+        <v>7.03125</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1014412416851441</v>
+        <v>0.1081210956271024</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.535714285714286</v>
+        <v>6.6875</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.71428571428572</v>
+        <v>21.09375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3215077605321508</v>
+        <v>0.3243632868813071</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7312326227988878</v>
+        <v>0.7263763352506163</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3738317757009346</v>
+        <v>0.3798882681564246</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3183673469387755</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3879781420765027</v>
+        <v>0.3733333333333334</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3155172413793103</v>
+        <v>0.3170370370370371</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.462465245597776</v>
+        <v>1.452752670501233</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.636734693877551</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.998689384010485</v>
+        <v>0.9933333333333333</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8447204968944099</v>
+        <v>0.8603351955307262</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9087947882736156</v>
+        <v>0.8908045977011494</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.74390243902439</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.357357357357357</v>
+        <v>1.399463806970509</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.417417417417417</v>
+        <v>5.579088471849866</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.774774774774775</v>
+        <v>6.978552278820375</v>
       </c>
     </row>
     <row r="7">
@@ -1419,153 +1419,153 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="D8" t="n">
+        <v>42</v>
+      </c>
+      <c r="E8" t="n">
+        <v>72</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" t="n">
+        <v>53</v>
+      </c>
+      <c r="H8" t="n">
         <v>36</v>
       </c>
-      <c r="E8" t="n">
-        <v>59</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
+        <v>48</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>54</v>
+      </c>
+      <c r="L8" t="n">
+        <v>27</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>78</v>
+      </c>
+      <c r="S8" t="n">
+        <v>49</v>
+      </c>
+      <c r="T8" t="n">
+        <v>157</v>
+      </c>
+      <c r="U8" t="n">
+        <v>19</v>
+      </c>
+      <c r="V8" t="n">
+        <v>35</v>
+      </c>
+      <c r="W8" t="n">
+        <v>17</v>
+      </c>
+      <c r="X8" t="n">
         <v>11</v>
       </c>
-      <c r="G8" t="n">
-        <v>43</v>
-      </c>
-      <c r="H8" t="n">
-        <v>24</v>
-      </c>
-      <c r="I8" t="n">
-        <v>34</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>44</v>
-      </c>
-      <c r="L8" t="n">
-        <v>21</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N8" t="n">
-        <v>13</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>15</v>
-      </c>
-      <c r="R8" t="n">
-        <v>68</v>
-      </c>
-      <c r="S8" t="n">
-        <v>39</v>
-      </c>
-      <c r="T8" t="n">
-        <v>120</v>
-      </c>
-      <c r="U8" t="n">
-        <v>16</v>
-      </c>
-      <c r="V8" t="n">
-        <v>24</v>
-      </c>
-      <c r="W8" t="n">
-        <v>11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6</v>
-      </c>
       <c r="Y8" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="Z8" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.667</v>
+        <v>0.697</v>
       </c>
       <c r="AB8" t="n">
         <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH8" t="n">
         <v>7</v>
       </c>
-      <c r="AG8" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>5</v>
-      </c>
       <c r="AI8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.312</v>
+        <v>0.35</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.222</v>
+        <v>0.212</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>365:58</t>
+          <t>432:33</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>131.96</v>
+        <v>164.12</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.515</v>
+        <v>0.504</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.551</v>
+        <v>0.554</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.978</v>
+        <v>0.987</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.114</v>
+        <v>0.11</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.235</v>
+        <v>0.288</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.733</v>
+        <v>0.722</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.168</v>
+        <v>0.178</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.064</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="AY8" t="n">
         <v>0.014</v>
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G9" t="n">
+        <v>75</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" t="n">
+        <v>34</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32</v>
+      </c>
+      <c r="K9" t="n">
+        <v>112</v>
+      </c>
+      <c r="L9" t="n">
+        <v>49</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>21</v>
       </c>
-      <c r="G9" t="n">
-        <v>66</v>
-      </c>
-      <c r="H9" t="n">
-        <v>22</v>
-      </c>
-      <c r="I9" t="n">
-        <v>31</v>
-      </c>
-      <c r="J9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>96</v>
-      </c>
-      <c r="L9" t="n">
-        <v>45</v>
-      </c>
-      <c r="M9" t="n">
-        <v>17</v>
-      </c>
-      <c r="N9" t="n">
-        <v>13</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>19</v>
-      </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R9" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T9" t="n">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="U9" t="n">
         <v>27</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="W9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="Z9" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.739</v>
+        <v>0.756</v>
       </c>
       <c r="AB9" t="n">
         <v>6</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
       <c r="AH9" t="n">
         <v>13</v>
       </c>
       <c r="AI9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.419</v>
+        <v>0.382</v>
       </c>
       <c r="AK9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.229</v>
+        <v>0.244</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>628:15</t>
+          <t>710:58</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>160.64</v>
+        <v>181.96</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.527</v>
+        <v>0.524</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.554</v>
+        <v>0.55</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.977</v>
+        <v>0.973</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.172</v>
+        <v>0.164</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.368</v>
+        <v>1.524</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.166</v>
+        <v>0.17</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="10">
@@ -1737,67 +1737,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>406</v>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E10" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H10" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="I10" t="n">
+        <v>191</v>
+      </c>
+      <c r="J10" t="n">
         <v>158</v>
       </c>
-      <c r="J10" t="n">
-        <v>134</v>
-      </c>
       <c r="K10" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="L10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="R10" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="S10" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="T10" t="n">
-        <v>428</v>
+        <v>530</v>
       </c>
       <c r="U10" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="V10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="W10" t="n">
         <v>27</v>
@@ -1806,87 +1806,87 @@
         <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="Z10" t="n">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.75</v>
+        <v>0.764</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="AE10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.375</v>
+        <v>0.407</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.231</v>
+        <v>0.263</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>556:07</t>
+          <t>642:01</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>373.52</v>
+        <v>430.04</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.427</v>
+        <v>0.451</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.538</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.894</v>
+        <v>0.944</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.169</v>
+        <v>0.163</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.531</v>
+        <v>0.569</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.127</v>
+        <v>2.257</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="AW10" t="n">
         <v>0.032</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.14</v>
+        <v>0.145</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.177</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="11">
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -2055,156 +2055,156 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
         <v>12</v>
       </c>
-      <c r="I12" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>16</v>
       </c>
-      <c r="J12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="Q12" t="n">
+        <v>16</v>
+      </c>
+      <c r="R12" t="n">
         <v>22</v>
       </c>
-      <c r="L12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M12" t="n">
-        <v>8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12</v>
-      </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
+        <v>31</v>
+      </c>
+      <c r="T12" t="n">
+        <v>157</v>
+      </c>
+      <c r="U12" t="n">
+        <v>21</v>
+      </c>
+      <c r="V12" t="n">
+        <v>22</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>35</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI12" t="n">
         <v>18</v>
       </c>
-      <c r="S12" t="n">
-        <v>19</v>
-      </c>
-      <c r="T12" t="n">
-        <v>80</v>
-      </c>
-      <c r="U12" t="n">
-        <v>17</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="AJ12" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AK12" t="n">
         <v>7</v>
       </c>
-      <c r="W12" t="n">
-        <v>8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AL12" t="n">
         <v>23</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AM12" t="n">
         <v>0.304</v>
       </c>
-      <c r="AH12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>194:44</t>
+          <t>291:38</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>106.04</v>
+        <v>151.32</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.437</v>
+        <v>0.52</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.468</v>
+        <v>0.547</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.83</v>
+        <v>0.978</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.113</v>
+        <v>0.106</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.138</v>
+        <v>0.163</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.254</v>
+        <v>0.243</v>
       </c>
       <c r="AW12" t="n">
         <v>0.06900000000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.122</v>
+        <v>0.133</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="13">
@@ -2214,156 +2214,156 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="D13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" t="n">
+        <v>78</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47</v>
+      </c>
+      <c r="G13" t="n">
+        <v>121</v>
+      </c>
+      <c r="H13" t="n">
         <v>38</v>
       </c>
-      <c r="E13" t="n">
+      <c r="I13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J13" t="n">
         <v>70</v>
       </c>
-      <c r="F13" t="n">
-        <v>38</v>
-      </c>
-      <c r="G13" t="n">
-        <v>104</v>
-      </c>
-      <c r="H13" t="n">
-        <v>37</v>
-      </c>
-      <c r="I13" t="n">
-        <v>39</v>
-      </c>
-      <c r="J13" t="n">
-        <v>63</v>
-      </c>
       <c r="K13" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L13" t="n">
         <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R13" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="S13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T13" t="n">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="U13" t="n">
+        <v>19</v>
+      </c>
+      <c r="V13" t="n">
+        <v>20</v>
+      </c>
+      <c r="W13" t="n">
         <v>16</v>
       </c>
-      <c r="V13" t="n">
-        <v>17</v>
-      </c>
-      <c r="W13" t="n">
-        <v>13</v>
-      </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="AB13" t="n">
         <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF13" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.469</v>
+        <v>0.457</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.556</v>
+        <v>0.545</v>
       </c>
       <c r="AK13" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AL13" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.347</v>
+        <v>0.373</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>548:22</t>
+          <t>611:58</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>218.16</v>
+        <v>247.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.546</v>
+        <v>0.555</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.594</v>
+        <v>0.598</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.041</v>
+        <v>1.046</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.213</v>
+        <v>0.191</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.333</v>
+        <v>2.258</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.186</v>
+        <v>0.19</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.067</v>
+        <v>0.074</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.082</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="14">
@@ -2373,64 +2373,64 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>27</v>
+      </c>
+      <c r="C14" t="n">
+        <v>113</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17</v>
+      </c>
+      <c r="F14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>28</v>
+      </c>
+      <c r="K14" t="n">
+        <v>18</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>23</v>
       </c>
-      <c r="C14" t="n">
-        <v>95</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" t="n">
-        <v>14</v>
-      </c>
-      <c r="F14" t="n">
-        <v>25</v>
-      </c>
-      <c r="G14" t="n">
-        <v>52</v>
-      </c>
-      <c r="H14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="Q14" t="n">
         <v>23</v>
       </c>
-      <c r="K14" t="n">
+      <c r="R14" t="n">
+        <v>37</v>
+      </c>
+      <c r="S14" t="n">
         <v>16</v>
       </c>
-      <c r="L14" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>21</v>
-      </c>
-      <c r="R14" t="n">
-        <v>29</v>
-      </c>
-      <c r="S14" t="n">
-        <v>13</v>
-      </c>
       <c r="T14" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
@@ -2442,13 +2442,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.643</v>
+        <v>0.647</v>
       </c>
       <c r="AB14" t="n">
         <v>4</v>
@@ -2460,69 +2460,69 @@
         <v>0.571</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AH14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.857</v>
+        <v>0.7</v>
       </c>
       <c r="AK14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.422</v>
+        <v>0.415</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>287:48</t>
+          <t>349:45</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>90.52</v>
+        <v>107.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.674</v>
+        <v>0.656</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.669</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.049</v>
+        <v>1.052</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.232</v>
+        <v>0.214</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.091</v>
+        <v>0.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.095</v>
+        <v>1.217</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.147</v>
+        <v>0.144</v>
       </c>
       <c r="AW14" t="n">
         <v>0.019</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
@@ -2672,16 +2672,16 @@
         <v>1.333</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.184</v>
+        <v>0.185</v>
       </c>
       <c r="AW15" t="n">
         <v>0.063</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="16">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2709,10 +2709,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2733,22 +2733,22 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2760,13 +2760,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2806,23 +2806,23 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:44</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.136</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.064</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.322</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
         <v>48</v>
@@ -2874,7 +2874,7 @@
         <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
         <v>17</v>
@@ -2898,13 +2898,13 @@
         <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U17" t="n">
         <v>4</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>161:52</t>
+          <t>168:55</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -2987,19 +2987,19 @@
         <v>0.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.714</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.144</v>
+        <v>0.139</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.114</v>
+        <v>0.109</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="18">
@@ -3009,100 +3009,100 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K18" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R18" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="S18" t="n">
+        <v>35</v>
+      </c>
+      <c r="T18" t="n">
+        <v>239</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10</v>
+      </c>
+      <c r="V18" t="n">
         <v>30</v>
       </c>
-      <c r="T18" t="n">
-        <v>183</v>
-      </c>
-      <c r="U18" t="n">
-        <v>8</v>
-      </c>
-      <c r="V18" t="n">
-        <v>24</v>
-      </c>
       <c r="W18" t="n">
+        <v>12</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>94</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AE18" t="n">
         <v>11</v>
       </c>
-      <c r="X18" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>76</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>7</v>
-      </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3114,51 +3114,51 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.429</v>
+        <v>0.423</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>394:08</t>
+          <t>482:44</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>122.2</v>
+        <v>161.72</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.587</v>
+        <v>0.608</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.602</v>
+        <v>0.617</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.146</v>
+        <v>1.15</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.049</v>
+        <v>0.068</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.184</v>
+        <v>0.172</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.167</v>
+        <v>1.636</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.145</v>
+        <v>0.157</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.143</v>
+        <v>0.156</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19">
@@ -3168,247 +3168,247 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
-        <v>452</v>
+        <v>505</v>
       </c>
       <c r="D19" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E19" t="n">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I19" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="J19" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M19" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R19" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="S19" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="T19" t="n">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="U19" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="V19" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="W19" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="X19" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>175</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>69</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI19" t="n">
         <v>22</v>
       </c>
-      <c r="Y19" t="n">
-        <v>153</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>191</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>66</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>20</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="AK19" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AL19" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.381</v>
+        <v>0.375</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>766:29</t>
+          <t>883:18</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>405.52</v>
+        <v>454.36</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.576</v>
+        <v>0.57</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.636</v>
+        <v>0.629</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.115</v>
+        <v>1.111</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.123</v>
+        <v>0.117</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.315</v>
+        <v>0.307</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.56</v>
+        <v>1.642</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.247</v>
+        <v>0.241</v>
       </c>
       <c r="AW19" t="n">
         <v>0.023</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.112</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>#32 F. MAURI</t>
+          <t>#25 Y. MORIN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>3</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="F20" t="n">
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="n">
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3417,63 +3417,63 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AO20" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AP20" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>06:01</t>
-        </is>
-      </c>
-      <c r="AO20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0.375</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>0.375</v>
+        <v>0.515</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.75</v>
+        <v>1.031</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -3482,263 +3482,263 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>#34 D. NIEBLA</t>
+          <t>#32 F. MAURI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="n">
-        <v>7</v>
-      </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="n">
         <v>3</v>
       </c>
-      <c r="I21" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AJ21" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="AO21" t="n">
         <v>4</v>
       </c>
-      <c r="Z21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>23:58</t>
-        </is>
-      </c>
-      <c r="AO21" t="n">
-        <v>11.2</v>
-      </c>
       <c r="AP21" t="n">
-        <v>0.111</v>
+        <v>0.375</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.223</v>
+        <v>0.375</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.446</v>
+        <v>0.75</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.218</v>
+        <v>0.312</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>#35 S. BIRGANDER</t>
+          <t>#34 D. NIEBLA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>167</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>132</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>244</v>
+        <v>-3</v>
       </c>
       <c r="U22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.662</v>
+        <v>0.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.569</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -3753,151 +3753,151 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>428:46</t>
+          <t>23:58</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>168.68</v>
+        <v>11.2</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.591</v>
+        <v>0.111</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.589</v>
+        <v>0.223</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.99</v>
+        <v>0.446</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.083</v>
+        <v>0.333</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.184</v>
+        <v>0.219</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.19</v>
+        <v>0.045</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.048</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>#44 A. TOMIC</t>
+          <t>#35 S. BIRGANDER</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C23" t="n">
-        <v>291</v>
+        <v>195</v>
       </c>
       <c r="D23" t="n">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="E23" t="n">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K23" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M23" t="n">
         <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R23" t="n">
+        <v>54</v>
+      </c>
+      <c r="S23" t="n">
         <v>36</v>
       </c>
-      <c r="S23" t="n">
-        <v>87</v>
-      </c>
       <c r="T23" t="n">
-        <v>403</v>
+        <v>284</v>
       </c>
       <c r="U23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V23" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="W23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="Z23" t="n">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.736</v>
+        <v>0.667</v>
       </c>
       <c r="AB23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AC23" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.406</v>
+        <v>0.556</v>
       </c>
       <c r="AE23" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AF23" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.467</v>
+        <v>0.263</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3909,207 +3909,207 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>456:11</t>
+          <t>492:34</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>272.2</v>
+        <v>192.76</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.593</v>
+        <v>0.592</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.069</v>
+        <v>1.012</v>
       </c>
       <c r="AS23" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AT23" t="n">
         <v>0.099</v>
       </c>
-      <c r="AT23" t="n">
-        <v>0.262</v>
-      </c>
       <c r="AU23" t="n">
-        <v>1.741</v>
+        <v>1.536</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.278</v>
+        <v>0.183</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.098</v>
+        <v>0.103</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.24</v>
+        <v>0.188</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.064</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>#88 A. HANGA</t>
+          <t>#44 A. TOMIC</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>291</v>
+      </c>
+      <c r="D24" t="n">
+        <v>115</v>
+      </c>
+      <c r="E24" t="n">
+        <v>205</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>55</v>
+      </c>
+      <c r="I24" t="n">
+        <v>80</v>
+      </c>
+      <c r="J24" t="n">
+        <v>47</v>
+      </c>
+      <c r="K24" t="n">
+        <v>101</v>
+      </c>
+      <c r="L24" t="n">
+        <v>40</v>
+      </c>
+      <c r="M24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>12</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>27</v>
       </c>
-      <c r="C24" t="n">
-        <v>167</v>
-      </c>
-      <c r="D24" t="n">
-        <v>45</v>
-      </c>
-      <c r="E24" t="n">
-        <v>71</v>
-      </c>
-      <c r="F24" t="n">
-        <v>19</v>
-      </c>
-      <c r="G24" t="n">
-        <v>81</v>
-      </c>
-      <c r="H24" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="Q24" t="n">
+        <v>27</v>
+      </c>
+      <c r="R24" t="n">
+        <v>36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>87</v>
+      </c>
+      <c r="T24" t="n">
+        <v>403</v>
+      </c>
+      <c r="U24" t="n">
+        <v>14</v>
+      </c>
+      <c r="V24" t="n">
+        <v>36</v>
+      </c>
+      <c r="W24" t="n">
+        <v>6</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>117</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>159</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>39</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>96</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF24" t="n">
         <v>30</v>
       </c>
-      <c r="J24" t="n">
-        <v>42</v>
-      </c>
-      <c r="K24" t="n">
-        <v>73</v>
-      </c>
-      <c r="L24" t="n">
-        <v>17</v>
-      </c>
-      <c r="M24" t="n">
-        <v>27</v>
-      </c>
-      <c r="N24" t="n">
-        <v>10</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>18</v>
-      </c>
-      <c r="R24" t="n">
-        <v>62</v>
-      </c>
-      <c r="S24" t="n">
-        <v>52</v>
-      </c>
-      <c r="T24" t="n">
-        <v>210</v>
-      </c>
-      <c r="U24" t="n">
-        <v>24</v>
-      </c>
-      <c r="V24" t="n">
-        <v>21</v>
-      </c>
-      <c r="W24" t="n">
-        <v>11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>67</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL24" t="n">
         <v>5</v>
       </c>
-      <c r="AF24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>60</v>
-      </c>
       <c r="AM24" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>584:46</t>
+          <t>456:11</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>183.2</v>
+        <v>272.2</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.484</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.505</v>
+        <v>0.593</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.912</v>
+        <v>1.069</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.132</v>
+        <v>0.262</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.333</v>
+        <v>1.741</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.146</v>
+        <v>0.28</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.032</v>
+        <v>0.099</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.135</v>
+        <v>0.239</v>
       </c>
       <c r="AY24" t="n">
         <v>0.054</v>
@@ -4118,160 +4118,160 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>#88 A. HANGA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K25" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>22</v>
+      </c>
+      <c r="R25" t="n">
+        <v>70</v>
+      </c>
+      <c r="S25" t="n">
+        <v>55</v>
+      </c>
+      <c r="T25" t="n">
+        <v>232</v>
+      </c>
+      <c r="U25" t="n">
         <v>24</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>668:54</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>204.08</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.505</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>0.902</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.318</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="26">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,19 +4323,19 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
         <v>0</v>
@@ -4440,144 +4440,144 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>2358</v>
+        <v>2743</v>
       </c>
       <c r="D27" t="n">
-        <v>624</v>
+        <v>715</v>
       </c>
       <c r="E27" t="n">
-        <v>1131</v>
+        <v>1291</v>
       </c>
       <c r="F27" t="n">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="G27" t="n">
-        <v>692</v>
+        <v>794</v>
       </c>
       <c r="H27" t="n">
-        <v>441</v>
+        <v>518</v>
       </c>
       <c r="I27" t="n">
-        <v>582</v>
+        <v>679</v>
       </c>
       <c r="J27" t="n">
-        <v>498</v>
+        <v>577</v>
       </c>
       <c r="K27" t="n">
-        <v>726</v>
+        <v>843</v>
       </c>
       <c r="L27" t="n">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="M27" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="N27" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="Q27" t="n">
+        <v>334</v>
+      </c>
+      <c r="R27" t="n">
+        <v>699</v>
+      </c>
+      <c r="S27" t="n">
+        <v>659</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3215</v>
+      </c>
+      <c r="U27" t="n">
+        <v>282</v>
+      </c>
+      <c r="V27" t="n">
+        <v>332</v>
+      </c>
+      <c r="W27" t="n">
+        <v>186</v>
+      </c>
+      <c r="X27" t="n">
+        <v>116</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>934</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1274</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>184</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>398</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>115</v>
+      </c>
+      <c r="AF27" t="n">
         <v>298</v>
       </c>
-      <c r="R27" t="n">
-        <v>614</v>
-      </c>
-      <c r="S27" t="n">
-        <v>581</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2735</v>
-      </c>
-      <c r="U27" t="n">
-        <v>251</v>
-      </c>
-      <c r="V27" t="n">
-        <v>275</v>
-      </c>
-      <c r="W27" t="n">
-        <v>159</v>
-      </c>
-      <c r="X27" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>803</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1102</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.729</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>170</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>364</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>92</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>247</v>
-      </c>
       <c r="AG27" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>191</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>0.372</v>
       </c>
-      <c r="AH27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>168</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.357</v>
-      </c>
       <c r="AK27" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="AL27" t="n">
-        <v>524</v>
+        <v>603</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.311</v>
+        <v>0.322</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2401.08</v>
+        <v>2741.76</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.526</v>
+        <v>0.534</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.982</v>
+        <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.242</v>
+        <v>0.248</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.547</v>
+        <v>1.612</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
@@ -4586,7 +4586,7 @@
         <v>0.06</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4599,150 +4599,150 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>2273</v>
+        <v>2605</v>
       </c>
       <c r="D28" t="n">
-        <v>524</v>
+        <v>601</v>
       </c>
       <c r="E28" t="n">
-        <v>1041</v>
+        <v>1181</v>
       </c>
       <c r="F28" t="n">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="G28" t="n">
-        <v>763</v>
+        <v>900</v>
       </c>
       <c r="H28" t="n">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="I28" t="n">
-        <v>604</v>
+        <v>674</v>
       </c>
       <c r="J28" t="n">
-        <v>452</v>
+        <v>522</v>
       </c>
       <c r="K28" t="n">
-        <v>700</v>
+        <v>799</v>
       </c>
       <c r="L28" t="n">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="M28" t="n">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="N28" t="n">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>333</v>
+        <v>373</v>
       </c>
       <c r="Q28" t="n">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="R28" t="n">
-        <v>591</v>
+        <v>670</v>
       </c>
       <c r="S28" t="n">
-        <v>611</v>
+        <v>696</v>
       </c>
       <c r="T28" t="n">
-        <v>2595</v>
+        <v>2972</v>
       </c>
       <c r="U28" t="n">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="V28" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="W28" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="X28" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="Y28" t="n">
-        <v>789</v>
+        <v>884</v>
       </c>
       <c r="Z28" t="n">
-        <v>1079</v>
+        <v>1217</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.731</v>
+        <v>0.726</v>
       </c>
       <c r="AB28" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="AC28" t="n">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.374</v>
+        <v>0.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AF28" t="n">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.318</v>
+        <v>0.321</v>
       </c>
       <c r="AH28" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="n">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.388</v>
+        <v>0.373</v>
       </c>
       <c r="AK28" t="n">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="AL28" t="n">
-        <v>580</v>
+        <v>675</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6425:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2402.76</v>
+        <v>2750.56</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.502</v>
+        <v>0.504</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.549</v>
+        <v>0.548</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.946</v>
+        <v>0.947</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.257</v>
+        <v>0.245</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.357</v>
+        <v>1.399</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AX28" t="n">
         <v>0.14</v>
@@ -4815,153 +4815,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>4.607</v>
+        <v>5.062</v>
       </c>
       <c r="D30" t="n">
-        <v>1.286</v>
+        <v>1.312</v>
       </c>
       <c r="E30" t="n">
-        <v>2.107</v>
+        <v>2.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.393</v>
+        <v>0.438</v>
       </c>
       <c r="G30" t="n">
-        <v>1.536</v>
+        <v>1.656</v>
       </c>
       <c r="H30" t="n">
-        <v>0.857</v>
+        <v>1.125</v>
       </c>
       <c r="I30" t="n">
-        <v>1.214</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
-        <v>0.393</v>
+        <v>0.406</v>
       </c>
       <c r="K30" t="n">
-        <v>1.571</v>
+        <v>1.688</v>
       </c>
       <c r="L30" t="n">
-        <v>0.75</v>
+        <v>0.844</v>
       </c>
       <c r="M30" t="n">
-        <v>0.393</v>
+        <v>0.438</v>
       </c>
       <c r="N30" t="n">
-        <v>0.464</v>
+        <v>0.469</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.536</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.536</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>2.429</v>
+        <v>2.438</v>
       </c>
       <c r="S30" t="n">
-        <v>1.393</v>
+        <v>1.531</v>
       </c>
       <c r="T30" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="U30" t="n">
-        <v>0.571</v>
+        <v>0.594</v>
       </c>
       <c r="V30" t="n">
-        <v>0.857</v>
+        <v>1.094</v>
       </c>
       <c r="W30" t="n">
-        <v>0.393</v>
+        <v>0.531</v>
       </c>
       <c r="X30" t="n">
-        <v>0.214</v>
+        <v>0.344</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.857</v>
+        <v>2.156</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.786</v>
+        <v>3.094</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.667</v>
+        <v>0.697</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.179</v>
+        <v>0.156</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.286</v>
+        <v>0.312</v>
       </c>
       <c r="AD30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0.625</v>
       </c>
-      <c r="AE30" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0.571</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>0.312</v>
+        <v>0.35</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.214</v>
+        <v>0.219</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.964</v>
+        <v>1.031</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.222</v>
+        <v>0.212</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>4.713</v>
+        <v>5.129</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.515</v>
+        <v>0.504</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.551</v>
+        <v>0.554</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.978</v>
+        <v>0.987</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.114</v>
+        <v>0.11</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.235</v>
+        <v>0.288</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.733</v>
+        <v>0.722</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.168</v>
+        <v>0.178</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.064</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="AY30" t="n">
         <v>0.014</v>
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>5.607</v>
+        <v>5.531</v>
       </c>
       <c r="D31" t="n">
-        <v>1.286</v>
+        <v>1.312</v>
       </c>
       <c r="E31" t="n">
-        <v>2.214</v>
+        <v>2.219</v>
       </c>
       <c r="F31" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.75</v>
       </c>
-      <c r="G31" t="n">
-        <v>2.357</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.786</v>
-      </c>
       <c r="I31" t="n">
-        <v>1.107</v>
+        <v>1.062</v>
       </c>
       <c r="J31" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.429</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.607</v>
+        <v>1.531</v>
       </c>
       <c r="M31" t="n">
-        <v>0.607</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0.464</v>
+        <v>0.438</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.679</v>
+        <v>0.656</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.679</v>
+        <v>0.656</v>
       </c>
       <c r="R31" t="n">
-        <v>2.607</v>
+        <v>2.688</v>
       </c>
       <c r="S31" t="n">
-        <v>1.107</v>
+        <v>1.094</v>
       </c>
       <c r="T31" t="n">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="U31" t="n">
-        <v>0.964</v>
+        <v>0.844</v>
       </c>
       <c r="V31" t="n">
-        <v>0.536</v>
+        <v>0.625</v>
       </c>
       <c r="W31" t="n">
-        <v>0.536</v>
+        <v>0.625</v>
       </c>
       <c r="X31" t="n">
-        <v>0.357</v>
+        <v>0.406</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.821</v>
+        <v>1.844</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.464</v>
+        <v>2.438</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.739</v>
+        <v>0.756</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.214</v>
+        <v>0.188</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.357</v>
+        <v>0.375</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.464</v>
+        <v>0.406</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.107</v>
+        <v>1.062</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.419</v>
+        <v>0.382</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.286</v>
+        <v>0.312</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.25</v>
+        <v>1.281</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.229</v>
+        <v>0.244</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:13</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.737</v>
+        <v>5.686</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.527</v>
+        <v>0.524</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.554</v>
+        <v>0.55</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.977</v>
+        <v>0.973</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.118</v>
+        <v>0.115</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.172</v>
+        <v>0.164</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.368</v>
+        <v>1.524</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.08</v>
+        <v>0.078</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.166</v>
+        <v>0.17</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="32">
@@ -5133,156 +5133,156 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C32" t="n">
-        <v>12.846</v>
+        <v>13.533</v>
       </c>
       <c r="D32" t="n">
-        <v>2.577</v>
+        <v>2.6</v>
       </c>
       <c r="E32" t="n">
-        <v>5.846</v>
+        <v>5.767</v>
       </c>
       <c r="F32" t="n">
-        <v>0.923</v>
+        <v>1.033</v>
       </c>
       <c r="G32" t="n">
-        <v>3.423</v>
+        <v>3.433</v>
       </c>
       <c r="H32" t="n">
-        <v>4.923</v>
+        <v>5.233</v>
       </c>
       <c r="I32" t="n">
-        <v>6.077</v>
+        <v>6.367</v>
       </c>
       <c r="J32" t="n">
-        <v>5.154</v>
+        <v>5.267</v>
       </c>
       <c r="K32" t="n">
-        <v>2.769</v>
+        <v>2.867</v>
       </c>
       <c r="L32" t="n">
-        <v>0.615</v>
+        <v>0.6</v>
       </c>
       <c r="M32" t="n">
-        <v>1.385</v>
+        <v>1.367</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.423</v>
+        <v>2.333</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.423</v>
+        <v>2.333</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>2.367</v>
       </c>
       <c r="S32" t="n">
-        <v>5.038</v>
+        <v>4.967</v>
       </c>
       <c r="T32" t="n">
-        <v>428</v>
+        <v>530</v>
       </c>
       <c r="U32" t="n">
         <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.385</v>
+        <v>1.367</v>
       </c>
       <c r="W32" t="n">
-        <v>1.038</v>
+        <v>0.9</v>
       </c>
       <c r="X32" t="n">
-        <v>0.923</v>
+        <v>0.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>6</v>
+        <v>6.367</v>
       </c>
       <c r="Z32" t="n">
-        <v>8</v>
+        <v>8.333</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.75</v>
+        <v>0.764</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.385</v>
+        <v>1.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.538</v>
+        <v>2.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.346</v>
+        <v>0.367</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.923</v>
+        <v>0.9</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.375</v>
+        <v>0.407</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.577</v>
+        <v>0.667</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.5</v>
+        <v>2.533</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.231</v>
+        <v>0.263</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>14.366</v>
+        <v>14.335</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.427</v>
+        <v>0.451</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.538</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.894</v>
+        <v>0.944</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.169</v>
+        <v>0.163</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.531</v>
+        <v>0.569</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.127</v>
+        <v>2.257</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="AW32" t="n">
         <v>0.032</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.14</v>
+        <v>0.145</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="33">
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="AW33" t="n">
         <v>0</v>
@@ -5451,40 +5451,40 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>12.333</v>
       </c>
       <c r="D34" t="n">
-        <v>3.625</v>
+        <v>3.833</v>
       </c>
       <c r="E34" t="n">
-        <v>7.25</v>
+        <v>6.833</v>
       </c>
       <c r="F34" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>3.625</v>
+        <v>3.417</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>2.333</v>
       </c>
       <c r="J34" t="n">
-        <v>1.125</v>
+        <v>1.083</v>
       </c>
       <c r="K34" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
         <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="N34" t="n">
         <v>1</v>
@@ -5493,114 +5493,114 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="T34" t="n">
+        <v>157</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="T34" t="n">
-        <v>80</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.125</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.875</v>
-      </c>
-      <c r="AG34" t="n">
+      <c r="AJ34" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.917</v>
+      </c>
+      <c r="AM34" t="n">
         <v>0.304</v>
       </c>
-      <c r="AH34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>24:20</t>
+          <t>24:18</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>13.255</v>
+        <v>12.61</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.437</v>
+        <v>0.52</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.468</v>
+        <v>0.547</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.83</v>
+        <v>0.978</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.113</v>
+        <v>0.106</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.138</v>
+        <v>0.163</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.254</v>
+        <v>0.243</v>
       </c>
       <c r="AW34" t="n">
         <v>0.06900000000000001</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.122</v>
+        <v>0.133</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="35">
@@ -5610,43 +5610,43 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>8.407</v>
+        <v>8.355</v>
       </c>
       <c r="D35" t="n">
-        <v>1.407</v>
+        <v>1.29</v>
       </c>
       <c r="E35" t="n">
-        <v>2.593</v>
+        <v>2.516</v>
       </c>
       <c r="F35" t="n">
-        <v>1.407</v>
+        <v>1.516</v>
       </c>
       <c r="G35" t="n">
-        <v>3.852</v>
+        <v>3.903</v>
       </c>
       <c r="H35" t="n">
-        <v>1.37</v>
+        <v>1.226</v>
       </c>
       <c r="I35" t="n">
-        <v>1.444</v>
+        <v>1.29</v>
       </c>
       <c r="J35" t="n">
-        <v>2.333</v>
+        <v>2.258</v>
       </c>
       <c r="K35" t="n">
-        <v>1.259</v>
+        <v>1.355</v>
       </c>
       <c r="L35" t="n">
-        <v>0.222</v>
+        <v>0.194</v>
       </c>
       <c r="M35" t="n">
-        <v>0.519</v>
+        <v>0.516</v>
       </c>
       <c r="N35" t="n">
-        <v>0.185</v>
+        <v>0.226</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5658,108 +5658,108 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1.926</v>
+        <v>1.935</v>
       </c>
       <c r="S35" t="n">
-        <v>1.519</v>
+        <v>1.387</v>
       </c>
       <c r="T35" t="n">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="U35" t="n">
-        <v>0.593</v>
+        <v>0.613</v>
       </c>
       <c r="V35" t="n">
-        <v>0.63</v>
+        <v>0.645</v>
       </c>
       <c r="W35" t="n">
-        <v>0.481</v>
+        <v>0.516</v>
       </c>
       <c r="X35" t="n">
-        <v>0.259</v>
+        <v>0.29</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.963</v>
+        <v>1.774</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.407</v>
+        <v>2.226</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.259</v>
+        <v>0.226</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.444</v>
+        <v>0.452</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.556</v>
+        <v>0.516</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.185</v>
+        <v>1.129</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.469</v>
+        <v>0.457</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.185</v>
+        <v>0.194</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.333</v>
+        <v>0.355</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.556</v>
+        <v>0.545</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.222</v>
+        <v>1.323</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.519</v>
+        <v>3.548</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.347</v>
+        <v>0.373</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>8.08</v>
+        <v>7.987</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.546</v>
+        <v>0.555</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.594</v>
+        <v>0.598</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.041</v>
+        <v>1.046</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.213</v>
+        <v>0.191</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.333</v>
+        <v>2.258</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.186</v>
+        <v>0.19</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.067</v>
+        <v>0.074</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="36">
@@ -5769,153 +5769,153 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C36" t="n">
-        <v>4.13</v>
+        <v>4.185</v>
       </c>
       <c r="D36" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="E36" t="n">
-        <v>0.609</v>
+        <v>0.63</v>
       </c>
       <c r="F36" t="n">
-        <v>1.087</v>
+        <v>1.074</v>
       </c>
       <c r="G36" t="n">
-        <v>2.261</v>
+        <v>2.333</v>
       </c>
       <c r="H36" t="n">
-        <v>0.261</v>
+        <v>0.296</v>
       </c>
       <c r="I36" t="n">
-        <v>0.348</v>
+        <v>0.37</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>1.037</v>
       </c>
       <c r="K36" t="n">
-        <v>0.696</v>
+        <v>0.667</v>
       </c>
       <c r="L36" t="n">
-        <v>0.217</v>
+        <v>0.222</v>
       </c>
       <c r="M36" t="n">
-        <v>0.217</v>
+        <v>0.333</v>
       </c>
       <c r="N36" t="n">
-        <v>0.217</v>
+        <v>0.259</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.913</v>
+        <v>0.852</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.913</v>
+        <v>0.852</v>
       </c>
       <c r="R36" t="n">
-        <v>1.261</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.593</v>
       </c>
       <c r="T36" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="U36" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.148</v>
       </c>
       <c r="V36" t="n">
-        <v>0.304</v>
+        <v>0.259</v>
       </c>
       <c r="W36" t="n">
-        <v>0.13</v>
+        <v>0.111</v>
       </c>
       <c r="X36" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.391</v>
+        <v>0.407</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.609</v>
+        <v>0.63</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.643</v>
+        <v>0.647</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.174</v>
+        <v>0.148</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.304</v>
+        <v>0.259</v>
       </c>
       <c r="AD36" t="n">
         <v>0.571</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.043</v>
+        <v>0.111</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.261</v>
+        <v>0.259</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.304</v>
+        <v>0.37</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.857</v>
+        <v>0.7</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.826</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.957</v>
+        <v>1.963</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.422</v>
+        <v>0.415</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>3.936</v>
+        <v>3.978</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.674</v>
+        <v>0.656</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.669</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.049</v>
+        <v>1.052</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.232</v>
+        <v>0.214</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.091</v>
+        <v>0.1</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.095</v>
+        <v>1.217</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.147</v>
+        <v>0.144</v>
       </c>
       <c r="AW36" t="n">
         <v>0.019</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="AY36" t="n">
         <v>0.035</v>
@@ -6068,13 +6068,13 @@
         <v>1.333</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.184</v>
+        <v>0.185</v>
       </c>
       <c r="AW37" t="n">
         <v>0.063</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="AY37" t="n">
         <v>0.015</v>
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -6105,10 +6105,10 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -6129,22 +6129,22 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -6156,13 +6156,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -6202,23 +6202,23 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AP38" t="n">
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.136</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.064</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="AT38" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>0.322</v>
       </c>
       <c r="AW38" t="n">
         <v>0</v>
@@ -6246,106 +6246,106 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1.714</v>
       </c>
       <c r="D39" t="n">
-        <v>0.792</v>
+        <v>0.679</v>
       </c>
       <c r="E39" t="n">
-        <v>1.292</v>
+        <v>1.107</v>
       </c>
       <c r="F39" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="G39" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="H39" t="n">
-        <v>0.292</v>
+        <v>0.25</v>
       </c>
       <c r="I39" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="T39" t="n">
+        <v>31</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0.75</v>
       </c>
-      <c r="J39" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.458</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>30</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.875</v>
-      </c>
       <c r="Z39" t="n">
-        <v>1.417</v>
+        <v>1.214</v>
       </c>
       <c r="AA39" t="n">
         <v>0.618</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.375</v>
+        <v>0.321</v>
       </c>
       <c r="AD39" t="n">
         <v>0.444</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.25</v>
+        <v>0.214</v>
       </c>
       <c r="AG39" t="n">
         <v>0.167</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="AJ39" t="n">
         <v>0.333</v>
@@ -6354,18 +6354,18 @@
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>2.08</v>
+        <v>1.783</v>
       </c>
       <c r="AP39" t="n">
         <v>0.586</v>
@@ -6383,19 +6383,19 @@
         <v>0.2</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.714</v>
+        <v>1</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.144</v>
+        <v>0.139</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.114</v>
+        <v>0.109</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="40">
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C40" t="n">
-        <v>5.833</v>
+        <v>6.643</v>
       </c>
       <c r="D40" t="n">
-        <v>1.958</v>
+        <v>2.321</v>
       </c>
       <c r="E40" t="n">
-        <v>3.25</v>
+        <v>3.714</v>
       </c>
       <c r="F40" t="n">
-        <v>0.375</v>
+        <v>0.393</v>
       </c>
       <c r="G40" t="n">
-        <v>1.042</v>
+        <v>1.071</v>
       </c>
       <c r="H40" t="n">
-        <v>0.792</v>
+        <v>0.821</v>
       </c>
       <c r="I40" t="n">
-        <v>1.25</v>
+        <v>1.357</v>
       </c>
       <c r="J40" t="n">
-        <v>0.542</v>
+        <v>0.643</v>
       </c>
       <c r="K40" t="n">
-        <v>2.167</v>
+        <v>2.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.417</v>
+        <v>1.393</v>
       </c>
       <c r="M40" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="N40" t="n">
-        <v>0.667</v>
+        <v>0.821</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.25</v>
+        <v>0.393</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.25</v>
+        <v>0.393</v>
       </c>
       <c r="R40" t="n">
-        <v>1.75</v>
+        <v>1.857</v>
       </c>
       <c r="S40" t="n">
         <v>1.25</v>
       </c>
       <c r="T40" t="n">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="U40" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>1.071</v>
       </c>
       <c r="W40" t="n">
-        <v>0.458</v>
+        <v>0.429</v>
       </c>
       <c r="X40" t="n">
         <v>0.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.167</v>
+        <v>2.286</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.167</v>
+        <v>3.357</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.681</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.292</v>
+        <v>0.464</v>
       </c>
       <c r="AC40" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="AF40" t="n">
         <v>0.75</v>
       </c>
-      <c r="AD40" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.583</v>
-      </c>
       <c r="AG40" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.375</v>
+        <v>0.393</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.875</v>
+        <v>0.929</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.429</v>
+        <v>0.423</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>5.092</v>
+        <v>5.776</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.587</v>
+        <v>0.608</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.602</v>
+        <v>0.617</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.146</v>
+        <v>1.15</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.049</v>
+        <v>0.068</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.184</v>
+        <v>0.172</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.167</v>
+        <v>1.636</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.145</v>
+        <v>0.157</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.096</v>
+        <v>0.091</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.143</v>
+        <v>0.156</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="41">
@@ -6564,202 +6564,202 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C41" t="n">
-        <v>16.741</v>
+        <v>16.29</v>
       </c>
       <c r="D41" t="n">
-        <v>3.519</v>
+        <v>3.516</v>
       </c>
       <c r="E41" t="n">
-        <v>6.296</v>
+        <v>6.419</v>
       </c>
       <c r="F41" t="n">
-        <v>2.037</v>
+        <v>1.935</v>
       </c>
       <c r="G41" t="n">
-        <v>5.111</v>
+        <v>4.839</v>
       </c>
       <c r="H41" t="n">
-        <v>3.593</v>
+        <v>3.452</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>3.839</v>
       </c>
       <c r="J41" t="n">
-        <v>2.889</v>
+        <v>2.806</v>
       </c>
       <c r="K41" t="n">
-        <v>1.259</v>
+        <v>1.226</v>
       </c>
       <c r="L41" t="n">
-        <v>0.593</v>
+        <v>0.581</v>
       </c>
       <c r="M41" t="n">
-        <v>0.852</v>
+        <v>0.968</v>
       </c>
       <c r="N41" t="n">
-        <v>0.778</v>
+        <v>0.71</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.852</v>
+        <v>1.71</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.852</v>
+        <v>1.71</v>
       </c>
       <c r="R41" t="n">
-        <v>2.185</v>
+        <v>2.258</v>
       </c>
       <c r="S41" t="n">
-        <v>3.296</v>
+        <v>3.323</v>
       </c>
       <c r="T41" t="n">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>1.806</v>
       </c>
       <c r="V41" t="n">
-        <v>1.519</v>
+        <v>1.516</v>
       </c>
       <c r="W41" t="n">
-        <v>1.37</v>
+        <v>1.387</v>
       </c>
       <c r="X41" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.806</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.667</v>
+        <v>5.645</v>
       </c>
       <c r="Z41" t="n">
-        <v>7.074</v>
+        <v>7.097</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.801</v>
+        <v>0.795</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.148</v>
+        <v>1.032</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.444</v>
+        <v>2.226</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.47</v>
+        <v>0.464</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.296</v>
+        <v>0.29</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.778</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.381</v>
+        <v>0.31</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.37</v>
+        <v>0.387</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.741</v>
+        <v>0.71</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.667</v>
+        <v>1.548</v>
       </c>
       <c r="AL41" t="n">
-        <v>4.37</v>
+        <v>4.129</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.381</v>
+        <v>0.375</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>28:23</t>
+          <t>28:29</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>15.019</v>
+        <v>14.657</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.576</v>
+        <v>0.57</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.636</v>
+        <v>0.629</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.115</v>
+        <v>1.111</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.123</v>
+        <v>0.117</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.315</v>
+        <v>0.307</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.56</v>
+        <v>1.642</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.247</v>
+        <v>0.241</v>
       </c>
       <c r="AW41" t="n">
         <v>0.023</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.048</v>
+        <v>0.046</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.117</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#32 F. MAURI (Per Game)</t>
+          <t>#25 Y. MORIN (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.167</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6774,16 +6774,16 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -6792,19 +6792,19 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6813,63 +6813,63 @@
         <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AP42" t="n">
         <v>0.333</v>
       </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
+      <c r="AQ42" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
         <v>0.667</v>
       </c>
-      <c r="AP42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
       <c r="AU42" t="n">
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -6878,47 +6878,47 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#34 D. NIEBLA (Per Game)</t>
+          <t>#32 F. MAURI (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>0.714</v>
+        <v>0.5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.167</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="G43" t="n">
-        <v>0.286</v>
+        <v>0.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6930,34 +6930,34 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -6972,169 +6972,169 @@
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.286</v>
+        <v>0.167</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
         <v>0</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>03:25</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>1.6</v>
+        <v>0.667</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.111</v>
+        <v>0.375</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.223</v>
+        <v>0.375</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.446</v>
+        <v>0.75</v>
       </c>
       <c r="AS43" t="n">
         <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.218</v>
+        <v>0.312</v>
       </c>
       <c r="AW43" t="n">
         <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#35 S. BIRGANDER (Per Game)</t>
+          <t>#34 D. NIEBLA (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>7.261</v>
+        <v>0.714</v>
       </c>
       <c r="D44" t="n">
-        <v>3.391</v>
+        <v>0.143</v>
       </c>
       <c r="E44" t="n">
-        <v>5.739</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="H44" t="n">
-        <v>0.478</v>
+        <v>0.429</v>
       </c>
       <c r="I44" t="n">
-        <v>0.957</v>
+        <v>0.714</v>
       </c>
       <c r="J44" t="n">
-        <v>1.609</v>
+        <v>0.143</v>
       </c>
       <c r="K44" t="n">
-        <v>3.261</v>
+        <v>0.143</v>
       </c>
       <c r="L44" t="n">
-        <v>1.739</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.261</v>
+        <v>0.143</v>
       </c>
       <c r="N44" t="n">
-        <v>1.217</v>
+        <v>0.143</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.174</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.174</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.087</v>
+        <v>0.714</v>
       </c>
       <c r="S44" t="n">
-        <v>1.348</v>
+        <v>0.429</v>
       </c>
       <c r="T44" t="n">
-        <v>244</v>
+        <v>-3</v>
       </c>
       <c r="U44" t="n">
-        <v>0.522</v>
+        <v>0.143</v>
       </c>
       <c r="V44" t="n">
-        <v>1.174</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.391</v>
+        <v>0.143</v>
       </c>
       <c r="X44" t="n">
-        <v>0.217</v>
+        <v>0.143</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.13</v>
+        <v>0.571</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.217</v>
+        <v>1.429</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.662</v>
+        <v>0.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.609</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.826</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.569</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.652</v>
+        <v>0.286</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
         <v>0</v>
@@ -7149,151 +7149,151 @@
         <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AM44" t="n">
         <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>03:25</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>7.334</v>
+        <v>1.6</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.591</v>
+        <v>0.111</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.589</v>
+        <v>0.223</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.99</v>
+        <v>0.446</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.083</v>
+        <v>0.333</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.184</v>
+        <v>0.219</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.19</v>
+        <v>0.045</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.06</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#44 A. TOMIC (Per Game)</t>
+          <t>#35 S. BIRGANDER (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C45" t="n">
-        <v>12.652</v>
+        <v>7.222</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>3.333</v>
       </c>
       <c r="E45" t="n">
-        <v>8.913</v>
+        <v>5.63</v>
       </c>
       <c r="F45" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.391</v>
+        <v>0.556</v>
       </c>
       <c r="I45" t="n">
-        <v>3.478</v>
+        <v>1.074</v>
       </c>
       <c r="J45" t="n">
-        <v>2.043</v>
+        <v>1.593</v>
       </c>
       <c r="K45" t="n">
-        <v>4.391</v>
+        <v>3.185</v>
       </c>
       <c r="L45" t="n">
-        <v>1.739</v>
+        <v>1.667</v>
       </c>
       <c r="M45" t="n">
-        <v>0.261</v>
+        <v>0.222</v>
       </c>
       <c r="N45" t="n">
-        <v>0.522</v>
+        <v>1.148</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.174</v>
+        <v>1.037</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.174</v>
+        <v>1.037</v>
       </c>
       <c r="R45" t="n">
-        <v>1.565</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>3.783</v>
+        <v>1.333</v>
       </c>
       <c r="T45" t="n">
-        <v>403</v>
+        <v>284</v>
       </c>
       <c r="U45" t="n">
-        <v>0.609</v>
+        <v>0.63</v>
       </c>
       <c r="V45" t="n">
-        <v>1.565</v>
+        <v>1.074</v>
       </c>
       <c r="W45" t="n">
-        <v>0.261</v>
+        <v>0.333</v>
       </c>
       <c r="X45" t="n">
-        <v>0.13</v>
+        <v>0.185</v>
       </c>
       <c r="Y45" t="n">
-        <v>5.087</v>
+        <v>2.222</v>
       </c>
       <c r="Z45" t="n">
-        <v>6.913</v>
+        <v>3.333</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.736</v>
+        <v>0.667</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.696</v>
+        <v>1.481</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.174</v>
+        <v>2.667</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.406</v>
+        <v>0.556</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.609</v>
+        <v>0.185</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.304</v>
+        <v>0.704</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.467</v>
+        <v>0.263</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
@@ -7305,369 +7305,369 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>11.835</v>
+        <v>7.139</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.593</v>
+        <v>0.592</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.069</v>
+        <v>1.012</v>
       </c>
       <c r="AS45" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AT45" t="n">
         <v>0.099</v>
       </c>
-      <c r="AT45" t="n">
-        <v>0.262</v>
-      </c>
       <c r="AU45" t="n">
-        <v>1.741</v>
+        <v>1.536</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.278</v>
+        <v>0.183</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.098</v>
+        <v>0.103</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.24</v>
+        <v>0.188</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.081</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#88 A. HANGA (Per Game)</t>
+          <t>#44 A. TOMIC (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C46" t="n">
-        <v>6.185</v>
+        <v>12.652</v>
       </c>
       <c r="D46" t="n">
-        <v>1.667</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>2.63</v>
+        <v>8.913</v>
       </c>
       <c r="F46" t="n">
-        <v>0.704</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0.217</v>
       </c>
       <c r="H46" t="n">
-        <v>0.741</v>
+        <v>2.391</v>
       </c>
       <c r="I46" t="n">
-        <v>1.111</v>
+        <v>3.478</v>
       </c>
       <c r="J46" t="n">
-        <v>1.556</v>
+        <v>2.043</v>
       </c>
       <c r="K46" t="n">
-        <v>2.704</v>
+        <v>4.391</v>
       </c>
       <c r="L46" t="n">
-        <v>0.63</v>
+        <v>1.739</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0.261</v>
       </c>
       <c r="N46" t="n">
-        <v>0.37</v>
+        <v>0.522</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.667</v>
+        <v>1.174</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.667</v>
+        <v>1.174</v>
       </c>
       <c r="R46" t="n">
-        <v>2.296</v>
+        <v>1.565</v>
       </c>
       <c r="S46" t="n">
-        <v>1.926</v>
+        <v>3.783</v>
       </c>
       <c r="T46" t="n">
-        <v>210</v>
+        <v>403</v>
       </c>
       <c r="U46" t="n">
-        <v>0.889</v>
+        <v>0.609</v>
       </c>
       <c r="V46" t="n">
-        <v>0.778</v>
+        <v>1.565</v>
       </c>
       <c r="W46" t="n">
-        <v>0.407</v>
+        <v>0.261</v>
       </c>
       <c r="X46" t="n">
-        <v>0.259</v>
+        <v>0.13</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.704</v>
+        <v>5.087</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.481</v>
+        <v>6.913</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.736</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.519</v>
+        <v>1.696</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.852</v>
+        <v>4.174</v>
       </c>
       <c r="AD46" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AE46" t="n">
         <v>0.609</v>
       </c>
-      <c r="AE46" t="n">
-        <v>0.185</v>
-      </c>
       <c r="AF46" t="n">
-        <v>0.407</v>
+        <v>1.304</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.455</v>
+        <v>0.467</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.148</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.556</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.222</v>
+        <v>0.217</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>6.785</v>
+        <v>11.835</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.484</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.505</v>
+        <v>0.593</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.912</v>
+        <v>1.069</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.132</v>
+        <v>0.262</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.333</v>
+        <v>1.741</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.146</v>
+        <v>0.28</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.032</v>
+        <v>0.099</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.135</v>
+        <v>0.239</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.056</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>#88 A. HANGA (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>5.935</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1.516</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>2.419</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.742</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1.032</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1.645</v>
       </c>
       <c r="K47" t="n">
-        <v>2.214</v>
+        <v>2.71</v>
       </c>
       <c r="L47" t="n">
-        <v>1.179</v>
+        <v>0.613</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>0.968</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>0.323</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.857</v>
+        <v>0.71</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="R47" t="n">
-        <v>0.07099999999999999</v>
+        <v>2.258</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.774</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.677</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.548</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.323</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>0.484</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.613</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>6.583</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>0.505</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>0.902</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2.318</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="48">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7704,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2.188</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.188</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,19 +7719,19 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
         <v>0</v>
@@ -7836,144 +7836,144 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>84.214</v>
+        <v>85.71899999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>22.286</v>
+        <v>22.344</v>
       </c>
       <c r="E49" t="n">
-        <v>40.393</v>
+        <v>40.344</v>
       </c>
       <c r="F49" t="n">
-        <v>7.964</v>
+        <v>8.281000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>24.714</v>
+        <v>24.812</v>
       </c>
       <c r="H49" t="n">
-        <v>15.75</v>
+        <v>16.188</v>
       </c>
       <c r="I49" t="n">
-        <v>20.786</v>
+        <v>21.219</v>
       </c>
       <c r="J49" t="n">
-        <v>17.786</v>
+        <v>18.031</v>
       </c>
       <c r="K49" t="n">
-        <v>25.929</v>
+        <v>26.344</v>
       </c>
       <c r="L49" t="n">
-        <v>10.821</v>
+        <v>10.719</v>
       </c>
       <c r="M49" t="n">
-        <v>5.964</v>
+        <v>6.062</v>
       </c>
       <c r="N49" t="n">
-        <v>5.536</v>
+        <v>5.594</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>11.5</v>
+        <v>11.188</v>
       </c>
       <c r="Q49" t="n">
-        <v>10.643</v>
+        <v>10.438</v>
       </c>
       <c r="R49" t="n">
-        <v>21.929</v>
+        <v>21.844</v>
       </c>
       <c r="S49" t="n">
-        <v>20.75</v>
+        <v>20.594</v>
       </c>
       <c r="T49" t="n">
-        <v>2735</v>
+        <v>3215</v>
       </c>
       <c r="U49" t="n">
-        <v>8.964</v>
+        <v>8.811999999999999</v>
       </c>
       <c r="V49" t="n">
-        <v>9.821</v>
+        <v>10.375</v>
       </c>
       <c r="W49" t="n">
-        <v>5.679</v>
+        <v>5.812</v>
       </c>
       <c r="X49" t="n">
-        <v>3.571</v>
+        <v>3.625</v>
       </c>
       <c r="Y49" t="n">
-        <v>28.679</v>
+        <v>29.188</v>
       </c>
       <c r="Z49" t="n">
-        <v>39.357</v>
+        <v>39.812</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.729</v>
+        <v>0.733</v>
       </c>
       <c r="AB49" t="n">
-        <v>6.071</v>
+        <v>5.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>13</v>
+        <v>12.438</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.467</v>
+        <v>0.462</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.286</v>
+        <v>3.594</v>
       </c>
       <c r="AF49" t="n">
-        <v>8.821</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="AG49" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>5.969</v>
+      </c>
+      <c r="AJ49" t="n">
         <v>0.372</v>
       </c>
-      <c r="AH49" t="n">
-        <v>2.143</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.357</v>
-      </c>
       <c r="AK49" t="n">
-        <v>5.821</v>
+        <v>6.062</v>
       </c>
       <c r="AL49" t="n">
-        <v>18.714</v>
+        <v>18.844</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.311</v>
+        <v>0.322</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>85.753</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.526</v>
+        <v>0.534</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.982</v>
+        <v>1</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.134</v>
+        <v>0.131</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.242</v>
+        <v>0.248</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.547</v>
+        <v>1.612</v>
       </c>
       <c r="AV49" t="n">
         <v>0.2</v>
@@ -7982,7 +7982,7 @@
         <v>0.06</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.141</v>
+        <v>0.142</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7995,153 +7995,153 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>81.179</v>
+        <v>81.40600000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>18.714</v>
+        <v>18.781</v>
       </c>
       <c r="E50" t="n">
-        <v>37.179</v>
+        <v>36.906</v>
       </c>
       <c r="F50" t="n">
-        <v>9.071</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>27.25</v>
+        <v>28.125</v>
       </c>
       <c r="H50" t="n">
-        <v>16.536</v>
+        <v>15.906</v>
       </c>
       <c r="I50" t="n">
-        <v>21.571</v>
+        <v>21.062</v>
       </c>
       <c r="J50" t="n">
-        <v>16.143</v>
+        <v>16.312</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>24.969</v>
       </c>
       <c r="L50" t="n">
-        <v>10.964</v>
+        <v>10.875</v>
       </c>
       <c r="M50" t="n">
-        <v>6.714</v>
+        <v>6.688</v>
       </c>
       <c r="N50" t="n">
-        <v>5.536</v>
+        <v>5.562</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>11.893</v>
+        <v>11.656</v>
       </c>
       <c r="Q50" t="n">
-        <v>11.214</v>
+        <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>21.107</v>
+        <v>20.938</v>
       </c>
       <c r="S50" t="n">
-        <v>21.821</v>
+        <v>21.75</v>
       </c>
       <c r="T50" t="n">
-        <v>2595</v>
+        <v>2972</v>
       </c>
       <c r="U50" t="n">
-        <v>9.714</v>
+        <v>9.625</v>
       </c>
       <c r="V50" t="n">
-        <v>9.964</v>
+        <v>9.688000000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>5.107</v>
+        <v>4.875</v>
       </c>
       <c r="X50" t="n">
-        <v>2.929</v>
+        <v>2.812</v>
       </c>
       <c r="Y50" t="n">
-        <v>28.179</v>
+        <v>27.625</v>
       </c>
       <c r="Z50" t="n">
-        <v>38.536</v>
+        <v>38.031</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.731</v>
+        <v>0.726</v>
       </c>
       <c r="AB50" t="n">
-        <v>4.286</v>
+        <v>4.25</v>
       </c>
       <c r="AC50" t="n">
-        <v>11.464</v>
+        <v>11.188</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.374</v>
+        <v>0.38</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.786</v>
+        <v>2.812</v>
       </c>
       <c r="AF50" t="n">
         <v>8.75</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.318</v>
+        <v>0.321</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.536</v>
+        <v>2.625</v>
       </c>
       <c r="AI50" t="n">
-        <v>6.536</v>
+        <v>7.031</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.388</v>
+        <v>0.373</v>
       </c>
       <c r="AK50" t="n">
-        <v>6.536</v>
+        <v>6.688</v>
       </c>
       <c r="AL50" t="n">
-        <v>20.714</v>
+        <v>21.094</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>200:00</t>
+          <t>200:46</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>85.813</v>
+        <v>85.955</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.502</v>
+        <v>0.504</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.549</v>
+        <v>0.548</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.946</v>
+        <v>0.947</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.257</v>
+        <v>0.245</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.357</v>
+        <v>1.399</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.2</v>
+        <v>0.201</v>
       </c>
       <c r="AW50" t="n">
         <v>0.061</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Joventut Badalona.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2398.76</v>
+        <v>2546.8</v>
       </c>
       <c r="C2" t="n">
-        <v>2400.66</v>
+        <v>2548.160000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>114.2602450992644</v>
+        <v>114.0430742182594</v>
       </c>
       <c r="E2" t="n">
-        <v>108.5118259145402</v>
+        <v>108.5489137259826</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5335731414868106</v>
+        <v>0.5349048050770625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1305730625583567</v>
+        <v>0.1324025036109774</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3003502626970228</v>
+        <v>0.2983471074380165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2484412470023981</v>
+        <v>0.2475067996373527</v>
       </c>
       <c r="J2" t="n">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="K2" t="n">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="L2" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="M2" t="n">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="N2" t="n">
-        <v>934</v>
+        <v>985</v>
       </c>
       <c r="O2" t="n">
-        <v>1274</v>
+        <v>1341</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6110311750599521</v>
+        <v>0.6078875793291024</v>
       </c>
       <c r="Q2" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="R2" t="n">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1908872901678657</v>
+        <v>0.1885766092475068</v>
       </c>
       <c r="T2" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="U2" t="n">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1429256594724221</v>
+        <v>0.1450589301903898</v>
       </c>
       <c r="W2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="X2" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09160671462829736</v>
+        <v>0.09383499546690843</v>
       </c>
       <c r="Z2" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AA2" t="n">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2892086330935252</v>
+        <v>0.2910244786944696</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7331240188383046</v>
+        <v>0.7345264727815063</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4623115577889447</v>
+        <v>0.46875</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3859060402684564</v>
+        <v>0.384375</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3717277486910995</v>
+        <v>0.357487922705314</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3217247097844113</v>
+        <v>0.3239875389408099</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.466248037676609</v>
+        <v>1.469052945563013</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7718120805369127</v>
+        <v>0.76875</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.001259445843829</v>
+        <v>0.9964664310954063</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7560321715817694</v>
+        <v>0.7752525252525253</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.967930029154519</v>
+        <v>0.9833795013850416</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.603448275862069</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.611731843575419</v>
+        <v>1.576623376623377</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.824022346368715</v>
+        <v>5.72987012987013</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.435754189944134</v>
+        <v>7.306493506493506</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.96124999999999</v>
+        <v>74.90588235294116</v>
       </c>
       <c r="C3" t="n">
-        <v>75.02062500000001</v>
+        <v>74.9458823529412</v>
       </c>
       <c r="D3" t="n">
-        <v>114.2602450992644</v>
+        <v>114.0430742182594</v>
       </c>
       <c r="E3" t="n">
-        <v>108.5118259145402</v>
+        <v>108.5489137259826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5335731414868106</v>
+        <v>0.5349048050770626</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1305730625583567</v>
+        <v>0.1324025036109774</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3003502626970228</v>
+        <v>0.2983471074380165</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2484412470023981</v>
+        <v>0.2475067996373527</v>
       </c>
       <c r="J3" t="n">
-        <v>8.8125</v>
+        <v>9.029411764705882</v>
       </c>
       <c r="K3" t="n">
-        <v>10.375</v>
+        <v>10.44117647058824</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8125</v>
+        <v>5.705882352941177</v>
       </c>
       <c r="M3" t="n">
-        <v>10.4375</v>
+        <v>10.58823529411765</v>
       </c>
       <c r="N3" t="n">
-        <v>29.1875</v>
+        <v>28.97058823529412</v>
       </c>
       <c r="O3" t="n">
-        <v>39.8125</v>
+        <v>39.44117647058823</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6110311750599521</v>
+        <v>0.6078875793291024</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.75</v>
+        <v>5.735294117647059</v>
       </c>
       <c r="R3" t="n">
-        <v>12.4375</v>
+        <v>12.23529411764706</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1908872901678657</v>
+        <v>0.1885766092475068</v>
       </c>
       <c r="T3" t="n">
-        <v>3.59375</v>
+        <v>3.617647058823529</v>
       </c>
       <c r="U3" t="n">
-        <v>9.3125</v>
+        <v>9.411764705882353</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1429256594724221</v>
+        <v>0.1450589301903899</v>
       </c>
       <c r="W3" t="n">
-        <v>2.21875</v>
+        <v>2.176470588235294</v>
       </c>
       <c r="X3" t="n">
-        <v>5.96875</v>
+        <v>6.088235294117647</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09160671462829736</v>
+        <v>0.09383499546690843</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.0625</v>
+        <v>6.117647058823529</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.84375</v>
+        <v>18.88235294117647</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2892086330935252</v>
+        <v>0.2910244786944697</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7331240188383046</v>
+        <v>0.7345264727815064</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4623115577889447</v>
+        <v>0.4687500000000001</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3859060402684564</v>
+        <v>0.384375</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3717277486910995</v>
+        <v>0.357487922705314</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3217247097844113</v>
+        <v>0.3239875389408099</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.466248037676609</v>
+        <v>1.469052945563013</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7718120805369127</v>
+        <v>0.7687499999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.001259445843829</v>
+        <v>0.9964664310954063</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7560321715817694</v>
+        <v>0.7752525252525253</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.967930029154519</v>
+        <v>0.9833795013850416</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.603448275862069</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.611731843575419</v>
+        <v>1.576623376623376</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.824022346368715</v>
+        <v>5.729870129870129</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.435754189944134</v>
+        <v>7.306493506493505</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2402.56</v>
+        <v>2549.52</v>
       </c>
       <c r="C4" t="n">
-        <v>2400.66</v>
+        <v>2548.160000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>108.5118259145402</v>
+        <v>108.5489137259826</v>
       </c>
       <c r="E4" t="n">
-        <v>114.2602450992644</v>
+        <v>114.0430742182594</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5036040365209035</v>
+        <v>0.5022461814914645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1356087487638881</v>
+        <v>0.1349914096375685</v>
       </c>
       <c r="H4" t="n">
-        <v>0.292191435768262</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2445939452186449</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="J4" t="n">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M4" t="n">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="N4" t="n">
-        <v>884</v>
+        <v>925</v>
       </c>
       <c r="O4" t="n">
-        <v>1217</v>
+        <v>1279</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5848149927919269</v>
+        <v>0.5745732255166217</v>
       </c>
       <c r="Q4" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="R4" t="n">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1720326765977895</v>
+        <v>0.1729559748427673</v>
       </c>
       <c r="T4" t="n">
+        <v>96</v>
+      </c>
+      <c r="U4" t="n">
+        <v>307</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1379155435759209</v>
+      </c>
+      <c r="W4" t="n">
         <v>90</v>
       </c>
-      <c r="U4" t="n">
-        <v>280</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1345506967803941</v>
-      </c>
-      <c r="W4" t="n">
-        <v>84</v>
-      </c>
       <c r="X4" t="n">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1081210956271024</v>
+        <v>0.110062893081761</v>
       </c>
       <c r="Z4" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="AA4" t="n">
-        <v>675</v>
+        <v>718</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3243632868813071</v>
+        <v>0.3225516621743037</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7263763352506163</v>
+        <v>0.7232212666145426</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.3798882681564246</v>
+        <v>0.3662337662337662</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3127035830618892</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3733333333333334</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3170370370370371</v>
+        <v>0.3259052924791087</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.452752670501233</v>
+        <v>1.446442533229085</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6254071661237784</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9933333333333333</v>
+        <v>1.009345794392523</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8603351955307262</v>
+        <v>0.8493506493506493</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.8908045977011494</v>
+        <v>0.90625</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.733333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.399463806970509</v>
+        <v>1.393939393939394</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.579088471849866</v>
+        <v>5.621212121212121</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.978552278820375</v>
+        <v>7.015151515151516</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.08</v>
+        <v>74.98588235294118</v>
       </c>
       <c r="C5" t="n">
-        <v>75.02062500000001</v>
+        <v>74.9458823529412</v>
       </c>
       <c r="D5" t="n">
-        <v>108.5118259145402</v>
+        <v>108.5489137259826</v>
       </c>
       <c r="E5" t="n">
-        <v>114.2602450992644</v>
+        <v>114.0430742182594</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5036040365209035</v>
+        <v>0.5022461814914645</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1356087487638881</v>
+        <v>0.1349914096375685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.292191435768262</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2445939452186449</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="J5" t="n">
-        <v>9.625</v>
+        <v>9.617647058823529</v>
       </c>
       <c r="K5" t="n">
-        <v>9.6875</v>
+        <v>10.23529411764706</v>
       </c>
       <c r="L5" t="n">
-        <v>4.875</v>
+        <v>4.735294117647059</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>27.625</v>
+        <v>27.20588235294118</v>
       </c>
       <c r="O5" t="n">
-        <v>38.03125</v>
+        <v>37.61764705882353</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5848149927919269</v>
+        <v>0.5745732255166217</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>4.147058823529412</v>
       </c>
       <c r="R5" t="n">
-        <v>11.1875</v>
+        <v>11.32352941176471</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1720326765977895</v>
+        <v>0.1729559748427673</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8125</v>
+        <v>2.823529411764706</v>
       </c>
       <c r="U5" t="n">
-        <v>8.75</v>
+        <v>9.029411764705882</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1345506967803941</v>
+        <v>0.1379155435759209</v>
       </c>
       <c r="W5" t="n">
-        <v>2.625</v>
+        <v>2.647058823529412</v>
       </c>
       <c r="X5" t="n">
-        <v>7.03125</v>
+        <v>7.205882352941177</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1081210956271024</v>
+        <v>0.110062893081761</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.6875</v>
+        <v>6.882352941176471</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.09375</v>
+        <v>21.11764705882353</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3243632868813071</v>
+        <v>0.3225516621743037</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7263763352506163</v>
+        <v>0.7232212666145427</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3798882681564246</v>
+        <v>0.3662337662337662</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3127035830618893</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3733333333333334</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3170370370370371</v>
+        <v>0.3259052924791087</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.452752670501233</v>
+        <v>1.446442533229085</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6254071661237786</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9933333333333333</v>
+        <v>1.009345794392523</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8603351955307262</v>
+        <v>0.8493506493506493</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.8908045977011494</v>
+        <v>0.9062499999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.733333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.399463806970509</v>
+        <v>1.393939393939394</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.579088471849866</v>
+        <v>5.621212121212121</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.978552278820375</v>
+        <v>7.015151515151516</v>
       </c>
     </row>
     <row r="7">
@@ -1419,34 +1419,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J8" t="n">
         <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L8" t="n">
         <v>27</v>
@@ -1467,16 +1467,16 @@
         <v>18</v>
       </c>
       <c r="R8" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="T8" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="U8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V8" t="n">
         <v>35</v>
@@ -1488,22 +1488,22 @@
         <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="Z8" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.697</v>
+        <v>0.705</v>
       </c>
       <c r="AB8" t="n">
         <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
@@ -1518,57 +1518,57 @@
         <v>7</v>
       </c>
       <c r="AI8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="AK8" t="n">
         <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.212</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>432:33</t>
+          <t>458:26</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>164.12</v>
+        <v>171.88</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.504</v>
+        <v>0.496</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.554</v>
+        <v>0.549</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.987</v>
+        <v>0.983</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.288</v>
+        <v>0.298</v>
       </c>
       <c r="AU8" t="n">
         <v>0.722</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="AX8" t="n">
         <v>0.135</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="9">
@@ -1578,40 +1578,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
         <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I9" t="n">
+        <v>37</v>
+      </c>
+      <c r="J9" t="n">
         <v>34</v>
       </c>
-      <c r="J9" t="n">
-        <v>32</v>
-      </c>
       <c r="K9" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" t="n">
         <v>14</v>
@@ -1620,25 +1620,25 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R9" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="S9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="T9" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="U9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="V9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="W9" t="n">
         <v>20</v>
@@ -1647,84 +1647,84 @@
         <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="Z9" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.756</v>
+        <v>0.767</v>
       </c>
       <c r="AB9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AH9" t="n">
         <v>13</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.382</v>
+        <v>0.333</v>
       </c>
       <c r="AK9" t="n">
         <v>10</v>
       </c>
       <c r="AL9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.244</v>
+        <v>0.233</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>710:58</t>
+          <t>762:11</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>181.96</v>
+        <v>202.28</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.524</v>
+        <v>0.522</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.55</v>
+        <v>0.547</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.973</v>
+        <v>0.964</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.115</v>
+        <v>0.119</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.164</v>
+        <v>0.16</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.524</v>
+        <v>1.417</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.078</v>
+        <v>0.074</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.17</v>
+        <v>0.173</v>
       </c>
       <c r="AY9" t="n">
         <v>0.035</v>
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="D10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F10" t="n">
         <v>31</v>
@@ -1755,13 +1755,13 @@
         <v>103</v>
       </c>
       <c r="H10" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I10" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="J10" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K10" t="n">
         <v>86</v>
@@ -1770,7 +1770,7 @@
         <v>18</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
         <v>14</v>
@@ -1779,25 +1779,25 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R10" t="n">
         <v>71</v>
       </c>
       <c r="S10" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="T10" t="n">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="U10" t="n">
         <v>60</v>
       </c>
       <c r="V10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W10" t="n">
         <v>27</v>
@@ -1806,31 +1806,31 @@
         <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="Z10" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.764</v>
+        <v>0.77</v>
       </c>
       <c r="AB10" t="n">
         <v>14</v>
       </c>
       <c r="AC10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.359</v>
+        <v>0.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="AH10" t="n">
         <v>11</v>
@@ -1852,41 +1852,41 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>642:01</t>
+          <t>661:39</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>430.04</v>
+        <v>437.68</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.944</v>
+        <v>0.95</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.163</v>
+        <v>0.162</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.569</v>
+        <v>0.582</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.257</v>
+        <v>2.296</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.314</v>
+        <v>0.311</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.145</v>
+        <v>0.139</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.181</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="11">
@@ -2055,156 +2055,156 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K12" t="n">
+        <v>44</v>
+      </c>
+      <c r="L12" t="n">
+        <v>21</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
         <v>13</v>
       </c>
-      <c r="K12" t="n">
-        <v>36</v>
-      </c>
-      <c r="L12" t="n">
-        <v>18</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N12" t="n">
-        <v>12</v>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R12" t="n">
         <v>22</v>
       </c>
       <c r="S12" t="n">
+        <v>33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>185</v>
+      </c>
+      <c r="U12" t="n">
         <v>31</v>
       </c>
-      <c r="T12" t="n">
-        <v>157</v>
-      </c>
-      <c r="U12" t="n">
-        <v>21</v>
-      </c>
       <c r="V12" t="n">
+        <v>23</v>
+      </c>
+      <c r="W12" t="n">
+        <v>14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI12" t="n">
         <v>22</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>35</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>0.278</v>
+        <v>0.318</v>
       </c>
       <c r="AK12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>291:38</t>
+          <t>334:31</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>151.32</v>
+        <v>175.08</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.52</v>
+        <v>0.528</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.547</v>
+        <v>0.551</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.978</v>
+        <v>0.982</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.106</v>
+        <v>0.109</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.163</v>
+        <v>0.155</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.895</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.243</v>
+        <v>0.246</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.133</v>
+        <v>0.14</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="13">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J13" t="n">
         <v>70</v>
       </c>
       <c r="K13" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
         <v>7</v>
@@ -2256,22 +2256,22 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R13" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="S13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T13" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="U13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V13" t="n">
         <v>20</v>
@@ -2283,10 +2283,10 @@
         <v>9</v>
       </c>
       <c r="Y13" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Z13" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AA13" t="n">
         <v>0.797</v>
@@ -2301,13 +2301,13 @@
         <v>0.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.457</v>
+        <v>0.474</v>
       </c>
       <c r="AH13" t="n">
         <v>6</v>
@@ -2319,51 +2319,51 @@
         <v>0.545</v>
       </c>
       <c r="AK13" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AL13" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>611:58</t>
+          <t>648:16</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>247.6</v>
+        <v>267.36</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.555</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.598</v>
+        <v>0.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.046</v>
+        <v>1.047</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.125</v>
+        <v>0.127</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.258</v>
+        <v>2.059</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.19</v>
+        <v>0.194</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AX13" t="n">
         <v>0.074</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.078</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="14">
@@ -2373,67 +2373,67 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>29</v>
+      </c>
+      <c r="C14" t="n">
+        <v>128</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" t="n">
+        <v>71</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33</v>
+      </c>
+      <c r="K14" t="n">
+        <v>21</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>27</v>
       </c>
-      <c r="C14" t="n">
-        <v>113</v>
-      </c>
-      <c r="D14" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>29</v>
-      </c>
-      <c r="G14" t="n">
-        <v>63</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" t="n">
-        <v>28</v>
-      </c>
-      <c r="K14" t="n">
-        <v>18</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="Q14" t="n">
+        <v>27</v>
+      </c>
+      <c r="R14" t="n">
+        <v>44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>110</v>
+      </c>
+      <c r="U14" t="n">
         <v>6</v>
       </c>
-      <c r="M14" t="n">
-        <v>9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>23</v>
-      </c>
-      <c r="R14" t="n">
-        <v>37</v>
-      </c>
-      <c r="S14" t="n">
-        <v>16</v>
-      </c>
-      <c r="T14" t="n">
-        <v>93</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4</v>
-      </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W14" t="n">
         <v>3</v>
@@ -2442,13 +2442,13 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.647</v>
+        <v>0.65</v>
       </c>
       <c r="AB14" t="n">
         <v>4</v>
@@ -2469,60 +2469,60 @@
         <v>0.667</v>
       </c>
       <c r="AH14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.7</v>
+        <v>0.571</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.415</v>
+        <v>0.439</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>349:45</t>
+          <t>390:42</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>107.4</v>
+        <v>121.28</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.656</v>
+        <v>0.669</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.669</v>
+        <v>0.679</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.052</v>
+        <v>1.055</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.214</v>
+        <v>0.223</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.217</v>
+        <v>1.222</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="15">
@@ -2678,7 +2678,7 @@
         <v>0.063</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="AY15" t="n">
         <v>0.008</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.322</v>
+        <v>0.323</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
         <v>48</v>
@@ -2996,7 +2996,7 @@
         <v>0.047</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="AY17" t="n">
         <v>0.007</v>
@@ -3009,67 +3009,67 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I18" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M18" t="n">
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R18" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="S18" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="T18" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="U18" t="n">
         <v>10</v>
       </c>
       <c r="V18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W18" t="n">
         <v>12</v>
@@ -3078,31 +3078,31 @@
         <v>7</v>
       </c>
       <c r="Y18" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="Z18" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.681</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.481</v>
+        <v>0.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.524</v>
+        <v>0.583</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3117,48 +3117,48 @@
         <v>11</v>
       </c>
       <c r="AL18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.423</v>
+        <v>0.379</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>482:44</t>
+          <t>518:01</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>161.72</v>
+        <v>176.48</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.608</v>
+        <v>0.615</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.617</v>
+        <v>0.622</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.15</v>
+        <v>1.145</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.172</v>
+        <v>0.174</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.636</v>
+        <v>1.429</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.157</v>
+        <v>0.16</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.156</v>
+        <v>0.154</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="19">
@@ -3168,156 +3168,156 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>33</v>
+      </c>
+      <c r="C19" t="n">
+        <v>523</v>
+      </c>
+      <c r="D19" t="n">
+        <v>113</v>
+      </c>
+      <c r="E19" t="n">
+        <v>210</v>
+      </c>
+      <c r="F19" t="n">
+        <v>63</v>
+      </c>
+      <c r="G19" t="n">
+        <v>156</v>
+      </c>
+      <c r="H19" t="n">
+        <v>108</v>
+      </c>
+      <c r="I19" t="n">
+        <v>122</v>
+      </c>
+      <c r="J19" t="n">
+        <v>93</v>
+      </c>
+      <c r="K19" t="n">
+        <v>39</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20</v>
+      </c>
+      <c r="M19" t="n">
         <v>31</v>
       </c>
-      <c r="C19" t="n">
-        <v>505</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="N19" t="n">
+        <v>26</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>56</v>
+      </c>
+      <c r="R19" t="n">
+        <v>74</v>
+      </c>
+      <c r="S19" t="n">
         <v>109</v>
       </c>
-      <c r="E19" t="n">
-        <v>199</v>
-      </c>
-      <c r="F19" t="n">
-        <v>60</v>
-      </c>
-      <c r="G19" t="n">
-        <v>150</v>
-      </c>
-      <c r="H19" t="n">
-        <v>107</v>
-      </c>
-      <c r="I19" t="n">
-        <v>119</v>
-      </c>
-      <c r="J19" t="n">
-        <v>87</v>
-      </c>
-      <c r="K19" t="n">
-        <v>38</v>
-      </c>
-      <c r="L19" t="n">
-        <v>18</v>
-      </c>
-      <c r="M19" t="n">
-        <v>30</v>
-      </c>
-      <c r="N19" t="n">
-        <v>22</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>53</v>
-      </c>
-      <c r="R19" t="n">
-        <v>70</v>
-      </c>
-      <c r="S19" t="n">
-        <v>103</v>
-      </c>
       <c r="T19" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="U19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="V19" t="n">
         <v>47</v>
       </c>
       <c r="W19" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y19" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Z19" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.795</v>
+        <v>0.791</v>
       </c>
       <c r="AB19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC19" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.464</v>
+        <v>0.459</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
       </c>
       <c r="AF19" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.31</v>
+        <v>0.273</v>
       </c>
       <c r="AH19" t="n">
         <v>12</v>
       </c>
       <c r="AI19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.545</v>
+        <v>0.522</v>
       </c>
       <c r="AK19" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AL19" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.375</v>
+        <v>0.383</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>883:18</t>
+          <t>933:55</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>454.36</v>
+        <v>475.68</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.57</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.111</v>
+        <v>1.099</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.307</v>
+        <v>0.295</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.642</v>
+        <v>1.661</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.241</v>
+        <v>0.239</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="20">
@@ -3327,98 +3327,98 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>13</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="AC20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
@@ -3442,38 +3442,38 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>25:22</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>3.88</v>
+        <v>14.2</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.515</v>
+        <v>0.598</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.031</v>
+        <v>0.775</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.309</v>
+        <v>0.263</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.383</v>
+        <v>0.133</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.183</v>
+        <v>0.126</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
         <v>5</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -3699,7 +3699,7 @@
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
@@ -3753,45 +3753,45 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>23:58</t>
+          <t>28:35</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.223</v>
+        <v>0.205</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.446</v>
+        <v>0.41</v>
       </c>
       <c r="AS22" t="n">
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.219</v>
+        <v>0.2</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="AY22" t="n">
         <v>0.001</v>
@@ -3804,16 +3804,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D23" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E23" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -3822,49 +3822,49 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K23" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L23" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M23" t="n">
         <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R23" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="S23" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="T23" t="n">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="U23" t="n">
         <v>17</v>
       </c>
       <c r="V23" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="W23" t="n">
         <v>9</v>
@@ -3873,31 +3873,31 @@
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="Z23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.667</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB23" t="n">
         <v>40</v>
       </c>
       <c r="AC23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
       <c r="AE23" t="n">
         <v>5</v>
       </c>
       <c r="AF23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3919,41 +3919,41 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>492:34</t>
+          <t>525:40</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>192.76</v>
+        <v>203.4</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.592</v>
+        <v>0.591</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.592</v>
+        <v>0.596</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.012</v>
+        <v>1.023</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.099</v>
+        <v>0.126</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.536</v>
+        <v>1.517</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.183</v>
+        <v>0.182</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="24">
@@ -4109,10 +4109,10 @@
         <v>0.099</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.239</v>
+        <v>0.236</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="25">
@@ -4122,43 +4122,43 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E25" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H25" t="n">
         <v>21</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J25" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K25" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L25" t="n">
         <v>19</v>
       </c>
       <c r="M25" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -4170,108 +4170,108 @@
         <v>22</v>
       </c>
       <c r="R25" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="S25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="T25" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="U25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="W25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z25" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.667</v>
+        <v>0.658</v>
       </c>
       <c r="AB25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.625</v>
+        <v>0.64</v>
       </c>
       <c r="AE25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.455</v>
+        <v>0.462</v>
       </c>
       <c r="AH25" t="n">
         <v>4</v>
       </c>
       <c r="AI25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.182</v>
+        <v>0.174</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.268</v>
+        <v>0.269</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>668:54</t>
+          <t>709:16</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>204.08</v>
+        <v>217.96</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.485</v>
+        <v>0.489</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.505</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.902</v>
+        <v>0.908</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.108</v>
+        <v>0.101</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.125</v>
+        <v>0.116</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.318</v>
+        <v>2.545</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.143</v>
+        <v>0.144</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AX25" t="n">
         <v>0.135</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="26">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4440,144 +4440,144 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2743</v>
+        <v>2906</v>
       </c>
       <c r="D27" t="n">
-        <v>715</v>
+        <v>757</v>
       </c>
       <c r="E27" t="n">
-        <v>1291</v>
+        <v>1357</v>
       </c>
       <c r="F27" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="G27" t="n">
-        <v>794</v>
+        <v>849</v>
       </c>
       <c r="H27" t="n">
-        <v>518</v>
+        <v>546</v>
       </c>
       <c r="I27" t="n">
-        <v>679</v>
+        <v>720</v>
       </c>
       <c r="J27" t="n">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="K27" t="n">
-        <v>843</v>
+        <v>896</v>
       </c>
       <c r="L27" t="n">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="M27" t="n">
+        <v>208</v>
+      </c>
+      <c r="N27" t="n">
+        <v>191</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>385</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>360</v>
+      </c>
+      <c r="R27" t="n">
+        <v>744</v>
+      </c>
+      <c r="S27" t="n">
+        <v>705</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3404</v>
+      </c>
+      <c r="U27" t="n">
+        <v>307</v>
+      </c>
+      <c r="V27" t="n">
+        <v>355</v>
+      </c>
+      <c r="W27" t="n">
         <v>194</v>
       </c>
-      <c r="N27" t="n">
-        <v>179</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>358</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>334</v>
-      </c>
-      <c r="R27" t="n">
-        <v>699</v>
-      </c>
-      <c r="S27" t="n">
-        <v>659</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3215</v>
-      </c>
-      <c r="U27" t="n">
-        <v>282</v>
-      </c>
-      <c r="V27" t="n">
-        <v>332</v>
-      </c>
-      <c r="W27" t="n">
-        <v>186</v>
-      </c>
       <c r="X27" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Y27" t="n">
-        <v>934</v>
+        <v>985</v>
       </c>
       <c r="Z27" t="n">
-        <v>1274</v>
+        <v>1341</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="AB27" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AC27" t="n">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.462</v>
+        <v>0.469</v>
       </c>
       <c r="AE27" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="AF27" t="n">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="AH27" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AI27" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.372</v>
+        <v>0.357</v>
       </c>
       <c r="AK27" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AL27" t="n">
-        <v>603</v>
+        <v>642</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2741.76</v>
+        <v>2907.8</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.534</v>
+        <v>0.535</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.575</v>
+        <v>0.576</v>
       </c>
       <c r="AR27" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="AT27" t="n">
         <v>0.248</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.612</v>
+        <v>1.577</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
@@ -4586,7 +4586,7 @@
         <v>0.06</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.142</v>
+        <v>0.14</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4599,150 +4599,150 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>2605</v>
+        <v>2766</v>
       </c>
       <c r="D28" t="n">
-        <v>601</v>
+        <v>632</v>
       </c>
       <c r="E28" t="n">
-        <v>1181</v>
+        <v>1263</v>
       </c>
       <c r="F28" t="n">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="G28" t="n">
-        <v>900</v>
+        <v>963</v>
       </c>
       <c r="H28" t="n">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="I28" t="n">
-        <v>674</v>
+        <v>708</v>
       </c>
       <c r="J28" t="n">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="K28" t="n">
-        <v>799</v>
+        <v>849</v>
       </c>
       <c r="L28" t="n">
+        <v>384</v>
+      </c>
+      <c r="M28" t="n">
+        <v>229</v>
+      </c>
+      <c r="N28" t="n">
+        <v>190</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>374</v>
+      </c>
+      <c r="R28" t="n">
+        <v>716</v>
+      </c>
+      <c r="S28" t="n">
+        <v>742</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3152</v>
+      </c>
+      <c r="U28" t="n">
+        <v>327</v>
+      </c>
+      <c r="V28" t="n">
         <v>348</v>
       </c>
-      <c r="M28" t="n">
-        <v>214</v>
-      </c>
-      <c r="N28" t="n">
-        <v>178</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>373</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>352</v>
-      </c>
-      <c r="R28" t="n">
-        <v>670</v>
-      </c>
-      <c r="S28" t="n">
-        <v>696</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2972</v>
-      </c>
-      <c r="U28" t="n">
-        <v>308</v>
-      </c>
-      <c r="V28" t="n">
-        <v>310</v>
-      </c>
       <c r="W28" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="X28" t="n">
+        <v>92</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>925</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1279</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>141</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>385</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>96</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>307</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AH28" t="n">
         <v>90</v>
       </c>
-      <c r="Y28" t="n">
-        <v>884</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1217</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>136</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>358</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>280</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>84</v>
-      </c>
       <c r="AI28" t="n">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.373</v>
+        <v>0.367</v>
       </c>
       <c r="AK28" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="AL28" t="n">
-        <v>675</v>
+        <v>718</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.317</v>
+        <v>0.326</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>6425:00</t>
+          <t>6825:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2750.56</v>
+        <v>2933.52</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.504</v>
+        <v>0.502</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.548</v>
+        <v>0.545</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.947</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.245</v>
+        <v>0.238</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.399</v>
+        <v>1.394</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="AX28" t="n">
         <v>0.14</v>
@@ -4815,156 +4815,156 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>5.062</v>
+        <v>4.971</v>
       </c>
       <c r="D30" t="n">
-        <v>1.312</v>
+        <v>1.294</v>
       </c>
       <c r="E30" t="n">
-        <v>2.25</v>
+        <v>2.206</v>
       </c>
       <c r="F30" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="G30" t="n">
-        <v>1.656</v>
+        <v>1.647</v>
       </c>
       <c r="H30" t="n">
-        <v>1.125</v>
+        <v>1.147</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.529</v>
       </c>
       <c r="J30" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="K30" t="n">
-        <v>1.688</v>
+        <v>1.706</v>
       </c>
       <c r="L30" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="M30" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="N30" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="R30" t="n">
-        <v>2.438</v>
+        <v>2.441</v>
       </c>
       <c r="S30" t="n">
-        <v>1.531</v>
+        <v>1.529</v>
       </c>
       <c r="T30" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="U30" t="n">
-        <v>0.594</v>
+        <v>0.647</v>
       </c>
       <c r="V30" t="n">
-        <v>1.094</v>
+        <v>1.029</v>
       </c>
       <c r="W30" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="X30" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.156</v>
+        <v>2.176</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.094</v>
+        <v>3.088</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.697</v>
+        <v>0.705</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AG30" t="n">
         <v>0.364</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.212</v>
+        <v>0.2</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>5.129</v>
+        <v>5.055</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.504</v>
+        <v>0.496</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.554</v>
+        <v>0.549</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.987</v>
+        <v>0.983</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.288</v>
+        <v>0.298</v>
       </c>
       <c r="AU30" t="n">
         <v>0.722</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="AX30" t="n">
         <v>0.135</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="31">
@@ -4974,153 +4974,153 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>5.531</v>
+        <v>5.735</v>
       </c>
       <c r="D31" t="n">
-        <v>1.312</v>
+        <v>1.471</v>
       </c>
       <c r="E31" t="n">
-        <v>2.219</v>
+        <v>2.353</v>
       </c>
       <c r="F31" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="G31" t="n">
-        <v>2.344</v>
+        <v>2.412</v>
       </c>
       <c r="H31" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="I31" t="n">
-        <v>1.062</v>
+        <v>1.088</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.647</v>
       </c>
       <c r="L31" t="n">
-        <v>1.531</v>
+        <v>1.471</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.656</v>
+        <v>0.706</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.656</v>
+        <v>0.706</v>
       </c>
       <c r="R31" t="n">
-        <v>2.688</v>
+        <v>2.706</v>
       </c>
       <c r="S31" t="n">
-        <v>1.094</v>
+        <v>1.118</v>
       </c>
       <c r="T31" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="U31" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="V31" t="n">
-        <v>0.625</v>
+        <v>0.676</v>
       </c>
       <c r="W31" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="X31" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.844</v>
+        <v>1.941</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.438</v>
+        <v>2.529</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.756</v>
+        <v>0.767</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.188</v>
+        <v>0.265</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.469</v>
+        <v>0.529</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.062</v>
+        <v>1.147</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.382</v>
+        <v>0.333</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.281</v>
+        <v>1.265</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.244</v>
+        <v>0.233</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.686</v>
+        <v>5.949</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.524</v>
+        <v>0.522</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.55</v>
+        <v>0.547</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.973</v>
+        <v>0.964</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.115</v>
+        <v>0.119</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.164</v>
+        <v>0.16</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.524</v>
+        <v>1.417</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.078</v>
+        <v>0.074</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.17</v>
+        <v>0.173</v>
       </c>
       <c r="AY31" t="n">
         <v>0.035</v>
@@ -5133,153 +5133,153 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>13.533</v>
+        <v>13.419</v>
       </c>
       <c r="D32" t="n">
-        <v>2.6</v>
+        <v>2.581</v>
       </c>
       <c r="E32" t="n">
-        <v>5.767</v>
+        <v>5.71</v>
       </c>
       <c r="F32" t="n">
-        <v>1.033</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>3.433</v>
+        <v>3.323</v>
       </c>
       <c r="H32" t="n">
-        <v>5.233</v>
+        <v>5.258</v>
       </c>
       <c r="I32" t="n">
-        <v>6.367</v>
+        <v>6.355</v>
       </c>
       <c r="J32" t="n">
-        <v>5.267</v>
+        <v>5.258</v>
       </c>
       <c r="K32" t="n">
-        <v>2.867</v>
+        <v>2.774</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6</v>
+        <v>0.581</v>
       </c>
       <c r="M32" t="n">
-        <v>1.367</v>
+        <v>1.419</v>
       </c>
       <c r="N32" t="n">
-        <v>0.467</v>
+        <v>0.452</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.333</v>
+        <v>2.29</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.333</v>
+        <v>2.29</v>
       </c>
       <c r="R32" t="n">
-        <v>2.367</v>
+        <v>2.29</v>
       </c>
       <c r="S32" t="n">
-        <v>4.967</v>
+        <v>4.935</v>
       </c>
       <c r="T32" t="n">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>1.935</v>
       </c>
       <c r="V32" t="n">
-        <v>1.367</v>
+        <v>1.387</v>
       </c>
       <c r="W32" t="n">
-        <v>0.9</v>
+        <v>0.871</v>
       </c>
       <c r="X32" t="n">
-        <v>0.8</v>
+        <v>0.774</v>
       </c>
       <c r="Y32" t="n">
-        <v>6.367</v>
+        <v>6.387</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.333</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.764</v>
+        <v>0.77</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.467</v>
+        <v>0.452</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.359</v>
+        <v>0.35</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.5</v>
+        <v>2.484</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.9</v>
+        <v>0.871</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.407</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.667</v>
+        <v>0.645</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.533</v>
+        <v>2.452</v>
       </c>
       <c r="AM32" t="n">
         <v>0.263</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>14.335</v>
+        <v>14.119</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.944</v>
+        <v>0.95</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.163</v>
+        <v>0.162</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.569</v>
+        <v>0.582</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.257</v>
+        <v>2.296</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.314</v>
+        <v>0.311</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.145</v>
+        <v>0.139</v>
       </c>
       <c r="AY32" t="n">
         <v>0.195</v>
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34" t="n">
-        <v>12.333</v>
+        <v>12.286</v>
       </c>
       <c r="D34" t="n">
-        <v>3.833</v>
+        <v>3.643</v>
       </c>
       <c r="E34" t="n">
-        <v>6.833</v>
+        <v>6.643</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>1.143</v>
       </c>
       <c r="G34" t="n">
-        <v>3.417</v>
+        <v>3.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.667</v>
+        <v>1.571</v>
       </c>
       <c r="I34" t="n">
-        <v>2.333</v>
+        <v>2.286</v>
       </c>
       <c r="J34" t="n">
-        <v>1.083</v>
+        <v>1.214</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>3.143</v>
       </c>
       <c r="L34" t="n">
         <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0.833</v>
+        <v>0.786</v>
       </c>
       <c r="N34" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.357</v>
+      </c>
+      <c r="T34" t="n">
+        <v>185</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="W34" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.583</v>
-      </c>
-      <c r="T34" t="n">
-        <v>157</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.917</v>
-      </c>
       <c r="X34" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.833</v>
+        <v>3.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.167</v>
+        <v>4.929</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.742</v>
+        <v>0.71</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.417</v>
+        <v>0.571</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.083</v>
+        <v>1.214</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.385</v>
+        <v>0.471</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.25</v>
+        <v>1.143</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.917</v>
+        <v>2.786</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.429</v>
+        <v>0.41</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.5</v>
+        <v>1.571</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.278</v>
+        <v>0.318</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.583</v>
+        <v>0.643</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.917</v>
+        <v>1.929</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.304</v>
+        <v>0.333</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>24:18</t>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>12.61</v>
+        <v>12.506</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.52</v>
+        <v>0.528</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.547</v>
+        <v>0.551</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.978</v>
+        <v>0.982</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.106</v>
+        <v>0.109</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.163</v>
+        <v>0.155</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.895</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.243</v>
+        <v>0.246</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.133</v>
+        <v>0.14</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.042</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="35">
@@ -5610,156 +5610,156 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>8.355</v>
+        <v>8.484999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>1.29</v>
+        <v>1.303</v>
       </c>
       <c r="E35" t="n">
-        <v>2.516</v>
+        <v>2.485</v>
       </c>
       <c r="F35" t="n">
-        <v>1.516</v>
+        <v>1.545</v>
       </c>
       <c r="G35" t="n">
-        <v>3.903</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>1.226</v>
+        <v>1.242</v>
       </c>
       <c r="I35" t="n">
-        <v>1.29</v>
+        <v>1.333</v>
       </c>
       <c r="J35" t="n">
-        <v>2.258</v>
+        <v>2.121</v>
       </c>
       <c r="K35" t="n">
-        <v>1.355</v>
+        <v>1.364</v>
       </c>
       <c r="L35" t="n">
-        <v>0.194</v>
+        <v>0.212</v>
       </c>
       <c r="M35" t="n">
-        <v>0.516</v>
+        <v>0.515</v>
       </c>
       <c r="N35" t="n">
-        <v>0.226</v>
+        <v>0.212</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="R35" t="n">
-        <v>1.935</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>1.387</v>
+        <v>1.364</v>
       </c>
       <c r="T35" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="U35" t="n">
-        <v>0.613</v>
+        <v>0.667</v>
       </c>
       <c r="V35" t="n">
-        <v>0.645</v>
+        <v>0.606</v>
       </c>
       <c r="W35" t="n">
-        <v>0.516</v>
+        <v>0.485</v>
       </c>
       <c r="X35" t="n">
-        <v>0.29</v>
+        <v>0.273</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.774</v>
+        <v>1.788</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.226</v>
+        <v>2.242</v>
       </c>
       <c r="AA35" t="n">
         <v>0.797</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.226</v>
+        <v>0.212</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.452</v>
+        <v>0.424</v>
       </c>
       <c r="AD35" t="n">
         <v>0.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.516</v>
+        <v>0.545</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.129</v>
+        <v>1.152</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.457</v>
+        <v>0.474</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.355</v>
+        <v>0.333</v>
       </c>
       <c r="AJ35" t="n">
         <v>0.545</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.323</v>
+        <v>1.364</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.548</v>
+        <v>3.667</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>7.987</v>
+        <v>8.102</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.555</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.598</v>
+        <v>0.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.046</v>
+        <v>1.047</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.125</v>
+        <v>0.127</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.258</v>
+        <v>2.059</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.19</v>
+        <v>0.194</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AX35" t="n">
         <v>0.074</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="36">
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C36" t="n">
-        <v>4.185</v>
+        <v>4.414</v>
       </c>
       <c r="D36" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="E36" t="n">
-        <v>0.63</v>
+        <v>0.621</v>
       </c>
       <c r="F36" t="n">
-        <v>1.074</v>
+        <v>1.138</v>
       </c>
       <c r="G36" t="n">
-        <v>2.333</v>
+        <v>2.448</v>
       </c>
       <c r="H36" t="n">
-        <v>0.296</v>
+        <v>0.31</v>
       </c>
       <c r="I36" t="n">
-        <v>0.37</v>
+        <v>0.414</v>
       </c>
       <c r="J36" t="n">
-        <v>1.037</v>
+        <v>1.138</v>
       </c>
       <c r="K36" t="n">
-        <v>0.667</v>
+        <v>0.724</v>
       </c>
       <c r="L36" t="n">
-        <v>0.222</v>
+        <v>0.241</v>
       </c>
       <c r="M36" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="N36" t="n">
-        <v>0.259</v>
+        <v>0.31</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.852</v>
+        <v>0.931</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.852</v>
+        <v>0.931</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>1.517</v>
       </c>
       <c r="S36" t="n">
-        <v>0.593</v>
+        <v>0.759</v>
       </c>
       <c r="T36" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="U36" t="n">
-        <v>0.148</v>
+        <v>0.207</v>
       </c>
       <c r="V36" t="n">
-        <v>0.259</v>
+        <v>0.379</v>
       </c>
       <c r="W36" t="n">
-        <v>0.111</v>
+        <v>0.103</v>
       </c>
       <c r="X36" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.407</v>
+        <v>0.448</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.647</v>
+        <v>0.65</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.259</v>
+        <v>0.241</v>
       </c>
       <c r="AD36" t="n">
         <v>0.571</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.111</v>
+        <v>0.103</v>
       </c>
       <c r="AG36" t="n">
         <v>0.667</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.259</v>
+        <v>0.276</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.37</v>
+        <v>0.483</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.7</v>
+        <v>0.571</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.862</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.963</v>
+        <v>1.966</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.415</v>
+        <v>0.439</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>3.978</v>
+        <v>4.182</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.656</v>
+        <v>0.669</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.669</v>
+        <v>0.679</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.052</v>
+        <v>1.055</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.214</v>
+        <v>0.223</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.217</v>
+        <v>1.222</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="37">
@@ -6074,7 +6074,7 @@
         <v>0.063</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="AY37" t="n">
         <v>0.015</v>
@@ -6227,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.322</v>
+        <v>0.323</v>
       </c>
       <c r="AW38" t="n">
         <v>0</v>
@@ -6246,106 +6246,106 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C39" t="n">
-        <v>1.714</v>
+        <v>1.6</v>
       </c>
       <c r="D39" t="n">
-        <v>0.679</v>
+        <v>0.633</v>
       </c>
       <c r="E39" t="n">
-        <v>1.107</v>
+        <v>1.033</v>
       </c>
       <c r="F39" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="G39" t="n">
-        <v>0.143</v>
+        <v>0.133</v>
       </c>
       <c r="H39" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="I39" t="n">
-        <v>0.643</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="K39" t="n">
-        <v>0.607</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="M39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="N39" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="R39" t="n">
-        <v>1.286</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="T39" t="n">
         <v>31</v>
       </c>
       <c r="U39" t="n">
-        <v>0.143</v>
+        <v>0.133</v>
       </c>
       <c r="V39" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="W39" t="n">
-        <v>0.179</v>
+        <v>0.167</v>
       </c>
       <c r="X39" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.214</v>
+        <v>1.133</v>
       </c>
       <c r="AA39" t="n">
         <v>0.618</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.143</v>
+        <v>0.133</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.321</v>
+        <v>0.3</v>
       </c>
       <c r="AD39" t="n">
         <v>0.444</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AG39" t="n">
         <v>0.167</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="AJ39" t="n">
         <v>0.333</v>
@@ -6354,18 +6354,18 @@
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>05:37</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>1.783</v>
+        <v>1.664</v>
       </c>
       <c r="AP39" t="n">
         <v>0.586</v>
@@ -6392,7 +6392,7 @@
         <v>0.047</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="AY39" t="n">
         <v>0.008</v>
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C40" t="n">
-        <v>6.643</v>
+        <v>6.733</v>
       </c>
       <c r="D40" t="n">
-        <v>2.321</v>
+        <v>2.4</v>
       </c>
       <c r="E40" t="n">
-        <v>3.714</v>
+        <v>3.7</v>
       </c>
       <c r="F40" t="n">
-        <v>0.393</v>
+        <v>0.367</v>
       </c>
       <c r="G40" t="n">
-        <v>1.071</v>
+        <v>1.1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.821</v>
+        <v>0.833</v>
       </c>
       <c r="I40" t="n">
-        <v>1.357</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0.643</v>
+        <v>0.667</v>
       </c>
       <c r="K40" t="n">
         <v>2.5</v>
       </c>
       <c r="L40" t="n">
-        <v>1.393</v>
+        <v>1.367</v>
       </c>
       <c r="M40" t="n">
-        <v>0.143</v>
+        <v>0.133</v>
       </c>
       <c r="N40" t="n">
-        <v>0.821</v>
+        <v>0.8</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.393</v>
+        <v>0.467</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.393</v>
+        <v>0.467</v>
       </c>
       <c r="R40" t="n">
-        <v>1.857</v>
+        <v>1.9</v>
       </c>
       <c r="S40" t="n">
-        <v>1.25</v>
+        <v>1.333</v>
       </c>
       <c r="T40" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="U40" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="V40" t="n">
-        <v>1.071</v>
+        <v>1.067</v>
       </c>
       <c r="W40" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="X40" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.286</v>
+        <v>2.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.357</v>
+        <v>3.367</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.681</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.464</v>
+        <v>0.467</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.964</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.481</v>
+        <v>0.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.393</v>
+        <v>0.467</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.524</v>
+        <v>0.583</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.143</v>
+        <v>0.133</v>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.393</v>
+        <v>0.367</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.929</v>
+        <v>0.967</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.423</v>
+        <v>0.379</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>5.776</v>
+        <v>5.883</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.608</v>
+        <v>0.615</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.617</v>
+        <v>0.622</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.15</v>
+        <v>1.145</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.068</v>
+        <v>0.079</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.172</v>
+        <v>0.174</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.636</v>
+        <v>1.429</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.157</v>
+        <v>0.16</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.156</v>
+        <v>0.154</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="41">
@@ -6564,156 +6564,156 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C41" t="n">
-        <v>16.29</v>
+        <v>15.848</v>
       </c>
       <c r="D41" t="n">
-        <v>3.516</v>
+        <v>3.424</v>
       </c>
       <c r="E41" t="n">
-        <v>6.419</v>
+        <v>6.364</v>
       </c>
       <c r="F41" t="n">
-        <v>1.935</v>
+        <v>1.909</v>
       </c>
       <c r="G41" t="n">
-        <v>4.839</v>
+        <v>4.727</v>
       </c>
       <c r="H41" t="n">
-        <v>3.452</v>
+        <v>3.273</v>
       </c>
       <c r="I41" t="n">
-        <v>3.839</v>
+        <v>3.697</v>
       </c>
       <c r="J41" t="n">
-        <v>2.806</v>
+        <v>2.818</v>
       </c>
       <c r="K41" t="n">
-        <v>1.226</v>
+        <v>1.182</v>
       </c>
       <c r="L41" t="n">
-        <v>0.581</v>
+        <v>0.606</v>
       </c>
       <c r="M41" t="n">
-        <v>0.968</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>0.71</v>
+        <v>0.788</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.71</v>
+        <v>1.697</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.71</v>
+        <v>1.697</v>
       </c>
       <c r="R41" t="n">
-        <v>2.258</v>
+        <v>2.242</v>
       </c>
       <c r="S41" t="n">
-        <v>3.323</v>
+        <v>3.303</v>
       </c>
       <c r="T41" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="U41" t="n">
-        <v>1.806</v>
+        <v>1.758</v>
       </c>
       <c r="V41" t="n">
-        <v>1.516</v>
+        <v>1.424</v>
       </c>
       <c r="W41" t="n">
-        <v>1.387</v>
+        <v>1.394</v>
       </c>
       <c r="X41" t="n">
-        <v>0.806</v>
+        <v>0.788</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.645</v>
+        <v>5.394</v>
       </c>
       <c r="Z41" t="n">
-        <v>7.097</v>
+        <v>6.818</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.795</v>
+        <v>0.791</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.032</v>
+        <v>1.03</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.226</v>
+        <v>2.242</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.464</v>
+        <v>0.459</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.29</v>
+        <v>0.273</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.9350000000000001</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.31</v>
+        <v>0.273</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.387</v>
+        <v>0.364</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.71</v>
+        <v>0.697</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.545</v>
+        <v>0.522</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.548</v>
+        <v>1.545</v>
       </c>
       <c r="AL41" t="n">
-        <v>4.129</v>
+        <v>4.03</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.375</v>
+        <v>0.383</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>28:29</t>
+          <t>28:18</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>14.657</v>
+        <v>14.415</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.57</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.111</v>
+        <v>1.099</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.307</v>
+        <v>0.295</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.642</v>
+        <v>1.661</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.241</v>
+        <v>0.239</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.111</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="42">
@@ -6723,16 +6723,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3.667</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>2.333</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -6741,10 +6741,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -6753,67 +6753,67 @@
         <v>1</v>
       </c>
       <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S42" t="n">
         <v>2</v>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="T42" t="n">
+        <v>13</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1</v>
       </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>4</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2</v>
-      </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -6838,38 +6838,38 @@
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>3.88</v>
+        <v>4.733</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.515</v>
+        <v>0.598</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.031</v>
+        <v>0.775</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>0.352</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.667</v>
+        <v>0.714</v>
       </c>
       <c r="AU42" t="n">
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.309</v>
+        <v>0.263</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.383</v>
+        <v>0.133</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.183</v>
+        <v>0.126</v>
       </c>
       <c r="AY42" t="n">
         <v>0</v>
@@ -7041,43 +7041,43 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="D44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="H44" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="I44" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="J44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="K44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="N44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="S44" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="T44" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="U44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="X44" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.429</v>
+        <v>1.25</v>
       </c>
       <c r="AA44" t="n">
         <v>0.4</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -7149,48 +7149,48 @@
         <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.286</v>
+        <v>0.375</v>
       </c>
       <c r="AM44" t="n">
         <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>03:25</t>
+          <t>03:34</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>1.6</v>
+        <v>1.525</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.223</v>
+        <v>0.205</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.446</v>
+        <v>0.41</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AU44" t="n">
         <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.219</v>
+        <v>0.2</v>
       </c>
       <c r="AW44" t="n">
         <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="45">
@@ -7200,16 +7200,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C45" t="n">
-        <v>7.222</v>
+        <v>7.172</v>
       </c>
       <c r="D45" t="n">
-        <v>3.333</v>
+        <v>3.241</v>
       </c>
       <c r="E45" t="n">
-        <v>5.63</v>
+        <v>5.483</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -7218,82 +7218,82 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.556</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>1.074</v>
+        <v>1.207</v>
       </c>
       <c r="J45" t="n">
-        <v>1.593</v>
+        <v>1.517</v>
       </c>
       <c r="K45" t="n">
-        <v>3.185</v>
+        <v>3.207</v>
       </c>
       <c r="L45" t="n">
-        <v>1.667</v>
+        <v>1.724</v>
       </c>
       <c r="M45" t="n">
-        <v>0.222</v>
+        <v>0.207</v>
       </c>
       <c r="N45" t="n">
-        <v>1.148</v>
+        <v>1.138</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.037</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.037</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>2.034</v>
       </c>
       <c r="S45" t="n">
-        <v>1.333</v>
+        <v>1.414</v>
       </c>
       <c r="T45" t="n">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="U45" t="n">
-        <v>0.63</v>
+        <v>0.586</v>
       </c>
       <c r="V45" t="n">
-        <v>1.074</v>
+        <v>1.207</v>
       </c>
       <c r="W45" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="X45" t="n">
-        <v>0.185</v>
+        <v>0.172</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.222</v>
+        <v>2.379</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.333</v>
+        <v>3.448</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.667</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.481</v>
+        <v>1.379</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.667</v>
+        <v>2.517</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.185</v>
+        <v>0.172</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.704</v>
+        <v>0.724</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
@@ -7315,41 +7315,41 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>7.139</v>
+        <v>7.014</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.592</v>
+        <v>0.591</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.592</v>
+        <v>0.596</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.012</v>
+        <v>1.023</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.099</v>
+        <v>0.126</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.536</v>
+        <v>1.517</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.183</v>
+        <v>0.182</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="46">
@@ -7505,7 +7505,7 @@
         <v>0.099</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.239</v>
+        <v>0.236</v>
       </c>
       <c r="AY46" t="n">
         <v>0.08</v>
@@ -7518,156 +7518,156 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C47" t="n">
-        <v>5.935</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>1.516</v>
+        <v>1.545</v>
       </c>
       <c r="E47" t="n">
-        <v>2.419</v>
+        <v>2.424</v>
       </c>
       <c r="F47" t="n">
-        <v>0.742</v>
+        <v>0.758</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>3.061</v>
       </c>
       <c r="H47" t="n">
-        <v>0.677</v>
+        <v>0.636</v>
       </c>
       <c r="I47" t="n">
-        <v>1.032</v>
+        <v>1.03</v>
       </c>
       <c r="J47" t="n">
-        <v>1.645</v>
+        <v>1.697</v>
       </c>
       <c r="K47" t="n">
-        <v>2.71</v>
+        <v>2.727</v>
       </c>
       <c r="L47" t="n">
-        <v>0.613</v>
+        <v>0.576</v>
       </c>
       <c r="M47" t="n">
-        <v>0.968</v>
+        <v>1.03</v>
       </c>
       <c r="N47" t="n">
-        <v>0.323</v>
+        <v>0.333</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.71</v>
+        <v>0.667</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.71</v>
+        <v>0.667</v>
       </c>
       <c r="R47" t="n">
-        <v>2.258</v>
+        <v>2.182</v>
       </c>
       <c r="S47" t="n">
-        <v>1.774</v>
+        <v>1.818</v>
       </c>
       <c r="T47" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="U47" t="n">
-        <v>0.774</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="V47" t="n">
-        <v>0.677</v>
+        <v>0.697</v>
       </c>
       <c r="W47" t="n">
-        <v>0.452</v>
+        <v>0.485</v>
       </c>
       <c r="X47" t="n">
-        <v>0.258</v>
+        <v>0.273</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.548</v>
+        <v>1.515</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.323</v>
+        <v>2.303</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.667</v>
+        <v>0.658</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.484</v>
+        <v>0.485</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.774</v>
+        <v>0.758</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.625</v>
+        <v>0.64</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.161</v>
+        <v>0.182</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.355</v>
+        <v>0.394</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.455</v>
+        <v>0.462</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.71</v>
+        <v>0.697</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.182</v>
+        <v>0.174</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.613</v>
+        <v>0.636</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.29</v>
+        <v>2.364</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.268</v>
+        <v>0.269</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>6.583</v>
+        <v>6.605</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.485</v>
+        <v>0.489</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.505</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.902</v>
+        <v>0.908</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.108</v>
+        <v>0.101</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.125</v>
+        <v>0.116</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.318</v>
+        <v>2.545</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.143</v>
+        <v>0.144</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="AX47" t="n">
         <v>0.135</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="48">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7704,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.188</v>
+        <v>2.118</v>
       </c>
       <c r="L48" t="n">
-        <v>1.188</v>
+        <v>1.176</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.75</v>
+        <v>0.735</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7836,144 +7836,144 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" t="n">
-        <v>85.71899999999999</v>
+        <v>85.471</v>
       </c>
       <c r="D49" t="n">
-        <v>22.344</v>
+        <v>22.265</v>
       </c>
       <c r="E49" t="n">
-        <v>40.344</v>
+        <v>39.912</v>
       </c>
       <c r="F49" t="n">
-        <v>8.281000000000001</v>
+        <v>8.294</v>
       </c>
       <c r="G49" t="n">
-        <v>24.812</v>
+        <v>24.971</v>
       </c>
       <c r="H49" t="n">
-        <v>16.188</v>
+        <v>16.059</v>
       </c>
       <c r="I49" t="n">
-        <v>21.219</v>
+        <v>21.176</v>
       </c>
       <c r="J49" t="n">
-        <v>18.031</v>
+        <v>17.853</v>
       </c>
       <c r="K49" t="n">
-        <v>26.344</v>
+        <v>26.353</v>
       </c>
       <c r="L49" t="n">
-        <v>10.719</v>
+        <v>10.618</v>
       </c>
       <c r="M49" t="n">
-        <v>6.062</v>
+        <v>6.118</v>
       </c>
       <c r="N49" t="n">
-        <v>5.594</v>
+        <v>5.618</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>11.188</v>
+        <v>11.324</v>
       </c>
       <c r="Q49" t="n">
-        <v>10.438</v>
+        <v>10.588</v>
       </c>
       <c r="R49" t="n">
-        <v>21.844</v>
+        <v>21.882</v>
       </c>
       <c r="S49" t="n">
-        <v>20.594</v>
+        <v>20.735</v>
       </c>
       <c r="T49" t="n">
-        <v>3215</v>
+        <v>3404</v>
       </c>
       <c r="U49" t="n">
-        <v>8.811999999999999</v>
+        <v>9.029</v>
       </c>
       <c r="V49" t="n">
-        <v>10.375</v>
+        <v>10.441</v>
       </c>
       <c r="W49" t="n">
-        <v>5.812</v>
+        <v>5.706</v>
       </c>
       <c r="X49" t="n">
-        <v>3.625</v>
+        <v>3.529</v>
       </c>
       <c r="Y49" t="n">
-        <v>29.188</v>
+        <v>28.971</v>
       </c>
       <c r="Z49" t="n">
-        <v>39.812</v>
+        <v>39.441</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.75</v>
+        <v>5.735</v>
       </c>
       <c r="AC49" t="n">
-        <v>12.438</v>
+        <v>12.235</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.462</v>
+        <v>0.469</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.594</v>
+        <v>3.618</v>
       </c>
       <c r="AF49" t="n">
-        <v>9.311999999999999</v>
+        <v>9.412000000000001</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.219</v>
+        <v>2.176</v>
       </c>
       <c r="AI49" t="n">
-        <v>5.969</v>
+        <v>6.088</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.372</v>
+        <v>0.357</v>
       </c>
       <c r="AK49" t="n">
-        <v>6.062</v>
+        <v>6.118</v>
       </c>
       <c r="AL49" t="n">
-        <v>18.844</v>
+        <v>18.882</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>85.68000000000001</v>
+        <v>85.524</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.534</v>
+        <v>0.535</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.575</v>
+        <v>0.576</v>
       </c>
       <c r="AR49" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="AT49" t="n">
         <v>0.248</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.612</v>
+        <v>1.577</v>
       </c>
       <c r="AV49" t="n">
         <v>0.2</v>
@@ -7982,7 +7982,7 @@
         <v>0.06</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.142</v>
+        <v>0.14</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7995,153 +7995,153 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
-        <v>81.40600000000001</v>
+        <v>81.35299999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>18.781</v>
+        <v>18.588</v>
       </c>
       <c r="E50" t="n">
-        <v>36.906</v>
+        <v>37.147</v>
       </c>
       <c r="F50" t="n">
-        <v>9.311999999999999</v>
+        <v>9.529</v>
       </c>
       <c r="G50" t="n">
-        <v>28.125</v>
+        <v>28.324</v>
       </c>
       <c r="H50" t="n">
-        <v>15.906</v>
+        <v>15.588</v>
       </c>
       <c r="I50" t="n">
-        <v>21.062</v>
+        <v>20.824</v>
       </c>
       <c r="J50" t="n">
-        <v>16.312</v>
+        <v>16.235</v>
       </c>
       <c r="K50" t="n">
-        <v>24.969</v>
+        <v>24.971</v>
       </c>
       <c r="L50" t="n">
-        <v>10.875</v>
+        <v>11.294</v>
       </c>
       <c r="M50" t="n">
-        <v>6.688</v>
+        <v>6.735</v>
       </c>
       <c r="N50" t="n">
-        <v>5.562</v>
+        <v>5.588</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>11.656</v>
+        <v>11.647</v>
       </c>
       <c r="Q50" t="n">
         <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>20.938</v>
+        <v>21.059</v>
       </c>
       <c r="S50" t="n">
-        <v>21.75</v>
+        <v>21.824</v>
       </c>
       <c r="T50" t="n">
-        <v>2972</v>
+        <v>3152</v>
       </c>
       <c r="U50" t="n">
-        <v>9.625</v>
+        <v>9.618</v>
       </c>
       <c r="V50" t="n">
-        <v>9.688000000000001</v>
+        <v>10.235</v>
       </c>
       <c r="W50" t="n">
-        <v>4.875</v>
+        <v>4.735</v>
       </c>
       <c r="X50" t="n">
-        <v>2.812</v>
+        <v>2.706</v>
       </c>
       <c r="Y50" t="n">
-        <v>27.625</v>
+        <v>27.206</v>
       </c>
       <c r="Z50" t="n">
-        <v>38.031</v>
+        <v>37.618</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.726</v>
+        <v>0.723</v>
       </c>
       <c r="AB50" t="n">
-        <v>4.25</v>
+        <v>4.147</v>
       </c>
       <c r="AC50" t="n">
-        <v>11.188</v>
+        <v>11.324</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.38</v>
+        <v>0.366</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.812</v>
+        <v>2.824</v>
       </c>
       <c r="AF50" t="n">
-        <v>8.75</v>
+        <v>9.029</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.321</v>
+        <v>0.313</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.625</v>
+        <v>2.647</v>
       </c>
       <c r="AI50" t="n">
-        <v>7.031</v>
+        <v>7.206</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.373</v>
+        <v>0.367</v>
       </c>
       <c r="AK50" t="n">
-        <v>6.688</v>
+        <v>6.882</v>
       </c>
       <c r="AL50" t="n">
-        <v>21.094</v>
+        <v>21.118</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.317</v>
+        <v>0.326</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>200:46</t>
+          <t>200:44</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>85.955</v>
+        <v>86.28</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.504</v>
+        <v>0.502</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.548</v>
+        <v>0.545</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.947</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.136</v>
+        <v>0.135</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.245</v>
+        <v>0.238</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.399</v>
+        <v>1.394</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.201</v>
+        <v>0.202</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.061</v>
+        <v>0.063</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
